--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.27</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>3.54</v>
+        <v>4.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.99</v>
+        <v>3.86</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>7.8</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>4.19</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>4.19</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>7.8</v>
+        <v>3.86</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="N19" t="n">
-        <v>3.86</v>
+        <v>7.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.27</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>4.19</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>4.19</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46069.22916666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,55 +1373,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.32</v>
+        <v>2.44</v>
       </c>
       <c r="M8" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.2</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46069.5</v>
+        <v>46069.43402777778</v>
       </c>
     </row>
     <row r="9">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46069.5</v>
@@ -1620,64 +1620,64 @@
         <v>4.64</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.89</v>
+        <v>4.78</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46069.52083333334</v>
+        <v>46069.5</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46069.54166666666</v>
+        <v>46069.52083333334</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46069.54166666666</v>
+        <v>46069.53472222222</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46069.5625</v>
+        <v>46069.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.62</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46069.58333333334</v>
+        <v>46069.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46069.58333333334</v>
+        <v>46069.5625</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46069.625</v>
+        <v>46069.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.9</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46069.625</v>
+        <v>46069.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="N19" t="n">
-        <v>7.8</v>
+        <v>3.53</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.55</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.27</v>
+        <v>2.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.47</v>
+        <v>2.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46069.64583333334</v>
+        <v>46069.625</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46069.66666666666</v>
+        <v>46069.625</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46069.66666666666</v>
+        <v>46069.64583333334</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,76 +3515,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46069.6875</v>
+        <v>46069.66666666666</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46069.6875</v>
+        <v>46069.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="M28" t="n">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="N28" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M32" t="n">
         <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>3.52</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46069.69791666666</v>
+        <v>46069.6875</v>
       </c>
     </row>
     <row r="33">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.09</v>
+        <v>4.96</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="N33" t="n">
-        <v>4.19</v>
+        <v>1.72</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46069.69791666666</v>
+        <v>46069.6875</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.93</v>
+        <v>3.05</v>
       </c>
       <c r="M34" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.61</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46069.70833333334</v>
+        <v>46069.69791666666</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46069.70833333334</v>
+        <v>46069.69791666666</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46069.71875</v>
+        <v>46069.70833333334</v>
       </c>
     </row>
     <row r="37">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46069.79166666666</v>
+        <v>46069.70833333334</v>
       </c>
     </row>
     <row r="38">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46069.875</v>
+        <v>46069.71875</v>
       </c>
     </row>
     <row r="39">
@@ -5021,116 +5021,354 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Harbour View</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="3" t="n">
+        <v>46069.8125</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AS Slimane</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ES Tunis</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="3" t="n">
+        <v>46069.875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Portmore United</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="3" t="n">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3" t="n">
         <v>46069.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.1</v>
+        <v>4.78</v>
       </c>
       <c r="M9" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>1.73</v>
       </c>
       <c r="O9" t="n">
-        <v>4.72</v>
+        <v>4.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>4.33</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.15</v>
-      </c>
-      <c r="V9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46069.5</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.74</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.46</v>
-      </c>
       <c r="S10" t="n">
-        <v>2.61</v>
+        <v>1.95</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="U10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.28</v>
       </c>
-      <c r="V10" t="n">
-        <v>9</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AC10" t="n">
-        <v>4.19</v>
+        <v>6.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.78</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>4.64</v>
       </c>
       <c r="O11" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>5.77</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="T11" t="n">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.96</v>
+        <v>4.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
         <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>1.98</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>7.62</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.48</v>
+        <v>7.5</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="T14" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
@@ -2129,31 +2129,31 @@
         <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="AD14" t="n">
         <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
         <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,40 +2206,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>7.62</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.69</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.5</v>
+        <v>4.48</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
@@ -2248,31 +2248,31 @@
         <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
         <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.42</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.53</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="V19" t="n">
-        <v>5.1</v>
+        <v>6.15</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.89</v>
+        <v>3.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.96</v>
+        <v>4.62</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="V20" t="n">
-        <v>5.95</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>2.19</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>3.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.07</v>
+        <v>1.36</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.61</v>
+        <v>2.23</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>3.53</v>
       </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.449999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="T22" t="n">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="V22" t="n">
-        <v>6.15</v>
+        <v>5.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.86</v>
+        <v>4.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.1</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.99</v>
-      </c>
       <c r="T23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z23" t="n">
         <v>4.05</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V23" t="n">
-        <v>13</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AA23" t="n">
-        <v>3.01</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE23" t="n">
-        <v>2.23</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.49</v>
+        <v>4.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="N26" t="n">
-        <v>2.32</v>
+        <v>1.52</v>
       </c>
       <c r="O26" t="n">
-        <v>2.95</v>
+        <v>4.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.69</v>
+        <v>1.98</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="V26" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>2.39</v>
       </c>
       <c r="M27" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="O27" t="n">
-        <v>4.75</v>
+        <v>2.73</v>
       </c>
       <c r="P27" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="V27" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="AA27" t="n">
         <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.96</v>
+        <v>2.93</v>
       </c>
       <c r="M33" t="n">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N33" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>4.19</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>4.19</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>4.64</v>
       </c>
       <c r="O10" t="n">
-        <v>4.72</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.36</v>
+        <v>5.77</v>
       </c>
       <c r="R10" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>1.95</v>
+        <v>2.61</v>
       </c>
       <c r="T10" t="n">
-        <v>4.33</v>
+        <v>3.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.1</v>
       </c>
-      <c r="AE10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.74</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.46</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.61</v>
+        <v>1.95</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="U11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.28</v>
       </c>
-      <c r="V11" t="n">
-        <v>9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AC11" t="n">
-        <v>4.19</v>
+        <v>6.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>7.62</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.5</v>
+        <v>4.48</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
@@ -2129,31 +2129,31 @@
         <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
         <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
         <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.42</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>6.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.69</v>
+        <v>2.06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.48</v>
+        <v>7.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="T15" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
         <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.25</v>
       </c>
-      <c r="M19" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH19" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M20" t="n">
         <v>3.1</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>2.75</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O20" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.55</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH21" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.53</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.8</v>
+        <v>3.61</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.52</v>
+        <v>2.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>4.62</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="V23" t="n">
-        <v>5.95</v>
+        <v>13</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.05</v>
+        <v>2.19</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>3.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.07</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.61</v>
+        <v>2.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>3.96</v>
       </c>
       <c r="P24" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
         <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.61</v>
+        <v>4.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="M25" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.64583333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.96</v>
+        <v>2.93</v>
       </c>
       <c r="M31" t="n">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N31" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>4.19</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.71875</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N2" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -686,43 +686,43 @@
         <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
         <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="AA2" t="n">
         <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD2" t="n">
         <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>2.2</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46069.43402777778</v>
+        <v>46069.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.78</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46069.5</v>
+        <v>46069.43402777778</v>
       </c>
     </row>
     <row r="10">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.74</v>
+        <v>4.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.64</v>
+        <v>1.66</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>5.62</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.77</v>
+        <v>2.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.19</v>
+        <v>3.96</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.98</v>
+        <v>1.15</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.37</v>
       </c>
-      <c r="O11" t="n">
-        <v>4.72</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.36</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>4.33</v>
+        <v>3.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="N12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T12" t="n">
         <v>4.33</v>
       </c>
-      <c r="O12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.35</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2.42</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46069.52083333334</v>
+        <v>46069.5</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46069.53472222222</v>
+        <v>46069.52083333334</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46069.54166666666</v>
+        <v>46069.53472222222</v>
       </c>
     </row>
     <row r="15">
@@ -2209,28 +2209,28 @@
         <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="O15" t="n">
         <v>2.06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
         <v>7.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>2.59</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="U15" t="n">
         <v>1.32</v>
@@ -2242,25 +2242,25 @@
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
         <v>2.05</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.7</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46069.5625</v>
+        <v>46069.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.92</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>2.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.57</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46069.58333333334</v>
+        <v>46069.5625</v>
       </c>
     </row>
     <row r="18">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46069.625</v>
+        <v>46069.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
         <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.25</v>
+        <v>3.33</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="N21" t="n">
-        <v>8.5</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.7</v>
+        <v>4.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.449999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>2.01</v>
       </c>
       <c r="T21" t="n">
-        <v>2.61</v>
+        <v>4.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="V21" t="n">
-        <v>6.15</v>
+        <v>13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.86</v>
+        <v>2.19</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>3.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.1</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="N22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.75</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.78</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.61</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.1</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>2.75</v>
+        <v>4.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.62</v>
+        <v>1.71</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.48</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>1.99</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>4.05</v>
+        <v>2.61</v>
       </c>
       <c r="U23" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>13</v>
+        <v>6.15</v>
       </c>
       <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.03</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.19</v>
+        <v>3.86</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.01</v>
+        <v>1.74</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>6</v>
+        <v>2.74</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.12</v>
       </c>
-      <c r="AE23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.35</v>
+        <v>1.91</v>
       </c>
       <c r="M24" t="n">
-        <v>3.46</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>2.03</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>3.96</v>
+        <v>2.44</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="V24" t="n">
-        <v>5.95</v>
+        <v>5.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z24" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.06</v>
+        <v>3.96</v>
       </c>
       <c r="P25" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.68</v>
+        <v>2.99</v>
       </c>
       <c r="T25" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>5.95</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.59</v>
+        <v>2.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
         <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46069.64583333334</v>
+        <v>46069.625</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,76 +3515,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>2.58</v>
       </c>
       <c r="M26" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="O26" t="n">
-        <v>4.75</v>
+        <v>3.06</v>
       </c>
       <c r="P26" t="n">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="R26" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>3.92</v>
+        <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V26" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46069.66666666666</v>
+        <v>46069.64583333334</v>
       </c>
     </row>
     <row r="27">
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
         <v>2.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.73</v>
+        <v>3.01</v>
       </c>
       <c r="P27" t="n">
         <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="R27" t="n">
         <v>1.17</v>
@@ -3658,31 +3658,31 @@
         <v>4.15</v>
       </c>
       <c r="T27" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.55</v>
+        <v>5.36</v>
       </c>
       <c r="AA27" t="n">
         <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="AC27" t="n">
         <v>2.17</v>
@@ -3694,10 +3694,10 @@
         <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="n">
         <v>1.48</v>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,76 +3753,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.04</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2.44</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46069.6875</v>
+        <v>46069.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="M30" t="n">
         <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.52</v>
+        <v>2.25</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.93</v>
+        <v>2.07</v>
       </c>
       <c r="M31" t="n">
-        <v>3.36</v>
+        <v>2.96</v>
       </c>
       <c r="N31" t="n">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,76 +4467,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>3.65</v>
+        <v>2.47</v>
       </c>
       <c r="O34" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.75</v>
+        <v>3.12</v>
       </c>
       <c r="R34" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>2.33</v>
+        <v>2.92</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46069.69791666666</v>
+        <v>46069.6875</v>
       </c>
     </row>
     <row r="35">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,76 +4705,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46069.70833333334</v>
+        <v>46069.69791666666</v>
       </c>
     </row>
     <row r="37">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.93</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,76 +4943,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="N38" t="n">
-        <v>2.45</v>
+        <v>3.61</v>
       </c>
       <c r="O38" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46069.71875</v>
+        <v>46069.70833333334</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,76 +5062,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46069.8125</v>
+        <v>46069.71875</v>
       </c>
     </row>
     <row r="40">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46069.875</v>
+        <v>46069.8125</v>
       </c>
     </row>
     <row r="41">
@@ -5259,116 +5259,235 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AS Slimane</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ES Tunis</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3" t="n">
+        <v>46069.875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Portmore United</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" s="3" t="n">
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3" t="n">
         <v>46069.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -668,7 +668,7 @@
         <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
         <v>2.23</v>
@@ -686,7 +686,7 @@
         <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
         <v>6</v>
@@ -707,7 +707,7 @@
         <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
         <v>2.83</v>
@@ -716,13 +716,13 @@
         <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
         <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
         <v>2.2</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.33</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>1.66</v>
+        <v>4.64</v>
       </c>
       <c r="O10" t="n">
-        <v>5.62</v>
+        <v>2.37</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AA10" t="n">
         <v>2.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
         <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.15</v>
+        <v>2.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.74</v>
+        <v>4.33</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.64</v>
+        <v>1.66</v>
       </c>
       <c r="O11" t="n">
-        <v>2.37</v>
+        <v>5.62</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA11" t="n">
         <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
         <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.05</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="M20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.3</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="P20" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.97</v>
+        <v>2.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.33</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>2.54</v>
+        <v>3.24</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="O21" t="n">
-        <v>4.21</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.01</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.19</v>
+        <v>3.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.01</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>6</v>
+        <v>2.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.23</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.39</v>
+        <v>3.33</v>
       </c>
       <c r="M22" t="n">
-        <v>3.12</v>
+        <v>2.54</v>
       </c>
       <c r="N22" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>4.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.01</v>
       </c>
       <c r="T22" t="n">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.11</v>
+        <v>3.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>3.35</v>
       </c>
       <c r="M23" t="n">
-        <v>4.95</v>
+        <v>3.46</v>
       </c>
       <c r="N23" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.71</v>
+        <v>3.96</v>
       </c>
       <c r="P23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>9.449999999999999</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="T23" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
         <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>6.15</v>
+        <v>5.95</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.86</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.24</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.6</v>
+        <v>1.29</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.12</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="O24" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="U24" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.33</v>
+        <v>1.69</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
         <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.35</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="n">
-        <v>3.46</v>
+        <v>4.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.96</v>
+        <v>1.71</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="U25" t="n">
         <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>6.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.05</v>
+        <v>3.86</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.29</v>
+        <v>3.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,19 +3515,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
         <v>2.73</v>
@@ -3539,10 +3539,10 @@
         <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V26" t="n">
         <v>4.4</v>
@@ -3554,7 +3554,7 @@
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z26" t="n">
         <v>5.5</v>
@@ -3566,7 +3566,7 @@
         <v>2.59</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
         <v>1.71</v>
@@ -3581,7 +3581,7 @@
         <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46069.64583333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.75</v>
+        <v>2.07</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>1.71</v>
+        <v>3.6</v>
       </c>
       <c r="O33" t="n">
-        <v>6.45</v>
+        <v>2.79</v>
       </c>
       <c r="P33" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.39</v>
+        <v>4.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="T33" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V33" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.25</v>
+        <v>2.23</v>
       </c>
       <c r="M37" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>1.4</v>
+        <v>3.04</v>
       </c>
       <c r="O37" t="n">
-        <v>5.75</v>
+        <v>2.38</v>
       </c>
       <c r="P37" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.77</v>
+        <v>3.68</v>
       </c>
       <c r="R37" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>4.9</v>
+        <v>3.28</v>
       </c>
       <c r="T37" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>4.43</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.93</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -692,7 +692,7 @@
         <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
         <v>1.05</v>
@@ -701,7 +701,7 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
         <v>1.75</v>
@@ -719,7 +719,7 @@
         <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46069.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.39</v>
+        <v>5.63</v>
       </c>
       <c r="M6" t="n">
-        <v>2.93</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.14</v>
+        <v>5.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.96</v>
+        <v>3.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1495,10 +1495,10 @@
         <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>2.37</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
         <v>5</v>
@@ -1641,7 +1641,7 @@
         <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
@@ -1650,31 +1650,31 @@
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
         <v>2.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
         <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
         <v>2.05</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.33</v>
+        <v>3.31</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="N11" t="n">
-        <v>1.66</v>
+        <v>2.52</v>
       </c>
       <c r="O11" t="n">
-        <v>5.62</v>
+        <v>4.61</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.33</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="T11" t="n">
-        <v>3.27</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.15</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="M12" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>1.66</v>
       </c>
       <c r="O12" t="n">
-        <v>4.72</v>
+        <v>5.62</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>2.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>4.33</v>
+        <v>3.27</v>
       </c>
       <c r="U12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.15</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1968,19 +1968,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
         <v>4.5</v>
@@ -1995,13 +1995,13 @@
         <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>8.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.09</v>
@@ -2010,28 +2010,28 @@
         <v>1.46</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
         <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
         <v>1.85</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,52 +2206,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.06</v>
+        <v>2.68</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.5</v>
+        <v>4.47</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
         <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
         <v>3.06</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AB15" t="n">
         <v>1.68</v>
@@ -2260,19 +2260,19 @@
         <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.47</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
         <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC16" t="n">
         <v>3.7</v>
@@ -2382,16 +2382,16 @@
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.65</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>3.46</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.44</v>
+        <v>3.96</v>
       </c>
       <c r="P20" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.25</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z20" t="n">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.24</v>
+        <v>4.95</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>8.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="P21" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH21" t="n">
         <v>3.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.33</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>2.54</v>
+        <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>4.21</v>
+        <v>2.44</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>2.01</v>
+        <v>3.34</v>
       </c>
       <c r="T22" t="n">
-        <v>4.05</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="V22" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.03</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.19</v>
+        <v>4.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.01</v>
+        <v>1.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>6</v>
+        <v>2.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.35</v>
+        <v>2.39</v>
       </c>
       <c r="M23" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>3.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>3.49</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.99</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>5.95</v>
+        <v>7.8</v>
       </c>
       <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.07</v>
       </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>4.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.01</v>
       </c>
       <c r="T24" t="n">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.11</v>
+        <v>2.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.26</v>
+        <v>2.35</v>
       </c>
       <c r="M25" t="n">
-        <v>4.95</v>
+        <v>3.24</v>
       </c>
       <c r="N25" t="n">
-        <v>8.5</v>
+        <v>2.84</v>
       </c>
       <c r="O25" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>9.449999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.86</v>
+        <v>3.28</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="O29" t="n">
-        <v>6.45</v>
+        <v>4.8</v>
       </c>
       <c r="P29" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S29" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T29" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
         <v>1.06</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.47</v>
       </c>
-      <c r="Z29" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC29" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.8</v>
+        <v>2.79</v>
       </c>
       <c r="P32" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.7</v>
+        <v>4.62</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>2.79</v>
+        <v>3.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.3</v>
+        <v>3.07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S33" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="T33" t="n">
         <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG33" t="n">
         <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="M35" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="P35" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.35</v>
+        <v>4.18</v>
       </c>
       <c r="R35" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="T35" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="U35" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="N36" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="O36" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.18</v>
+        <v>3.35</v>
       </c>
       <c r="R36" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S36" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="T36" t="n">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="U36" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V36" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z36" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AC36" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.23</v>
+        <v>6.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3.04</v>
+        <v>1.4</v>
       </c>
       <c r="O37" t="n">
-        <v>2.38</v>
+        <v>5.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.68</v>
+        <v>1.77</v>
       </c>
       <c r="R37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA37" t="n">
         <v>1.33</v>
       </c>
-      <c r="S37" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AB37" t="n">
-        <v>2.19</v>
+        <v>3.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.66</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.25</v>
+        <v>2.23</v>
       </c>
       <c r="M38" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.4</v>
+        <v>3.04</v>
       </c>
       <c r="O38" t="n">
-        <v>5.75</v>
+        <v>2.38</v>
       </c>
       <c r="P38" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.77</v>
+        <v>3.68</v>
       </c>
       <c r="R38" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>4.9</v>
+        <v>3.28</v>
       </c>
       <c r="T38" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="U38" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>4.43</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5062,28 +5062,28 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="O39" t="n">
         <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q39" t="n">
         <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S39" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="T39" t="n">
         <v>3.22</v>
@@ -5092,7 +5092,7 @@
         <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
         <v>1.01</v>
@@ -5101,34 +5101,34 @@
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z39" t="n">
         <v>2.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
         <v>3.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46069.71875</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,61 +1611,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.74</v>
+        <v>4.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.64</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.37</v>
+        <v>5.67</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>2.31</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
         <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
         <v>2.05</v>
@@ -1674,10 +1674,10 @@
         <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.05</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.33</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>1.66</v>
+        <v>4.64</v>
       </c>
       <c r="O12" t="n">
-        <v>5.62</v>
+        <v>2.37</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
         <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.15</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1986,16 +1986,16 @@
         <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
         <v>9.5</v>
@@ -2007,10 +2007,10 @@
         <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
         <v>2.42</v>
@@ -2025,16 +2025,16 @@
         <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
         <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46069.52083333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,55 +2206,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.47</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
         <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC15" t="n">
         <v>3.7</v>
@@ -2263,16 +2263,16 @@
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.46</v>
       </c>
       <c r="S16" t="n">
         <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
         <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2444,61 +2444,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
         <v>3.9</v>
       </c>
       <c r="O17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.26</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
         <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
         <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
         <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
         <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
         <v>1.56</v>
@@ -2507,10 +2507,10 @@
         <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46069.5625</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.99</v>
+        <v>4.75</v>
       </c>
       <c r="R18" t="n">
         <v>1.41</v>
@@ -2587,25 +2587,25 @@
         <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AA18" t="n">
         <v>2.06</v>
@@ -2614,22 +2614,22 @@
         <v>1.84</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O20" t="n">
         <v>3.96</v>
@@ -2816,7 +2816,7 @@
         <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
@@ -2837,22 +2837,22 @@
         <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
         <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="AA20" t="n">
         <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD20" t="n">
         <v>1.36</v>
@@ -2861,10 +2861,10 @@
         <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
         <v>1.29</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>4.95</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>8.5</v>
+        <v>2.84</v>
       </c>
       <c r="O21" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.449999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="T21" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.86</v>
+        <v>3.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.58</v>
+        <v>2.07</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.44</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>3.49</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.33</v>
+        <v>1.69</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.39</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.88</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.18</v>
+        <v>1.71</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.49</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V23" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.02</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.42</v>
+        <v>3.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="M25" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="P25" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>4.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="W25" t="n">
         <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.28</v>
+        <v>4.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="N27" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O27" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
         <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="R27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.17</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.14</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.36</v>
+        <v>5.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="N28" t="n">
         <v>1.49</v>
@@ -3771,10 +3771,10 @@
         <v>1.98</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="T28" t="n">
         <v>2.02</v>
@@ -3798,16 +3798,16 @@
         <v>5.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE28" t="n">
         <v>1.49</v>
@@ -3816,10 +3816,10 @@
         <v>2.44</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.52</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T29" t="n">
         <v>3.2</v>
       </c>
-      <c r="N29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.02</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.41</v>
+        <v>2.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.36</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="M31" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="N31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.75</v>
       </c>
-      <c r="O31" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.1</v>
+        <v>3.33</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="O33" t="n">
-        <v>3.76</v>
+        <v>4.8</v>
       </c>
       <c r="P33" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.07</v>
+        <v>2.45</v>
       </c>
       <c r="R33" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S33" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.1</v>
+        <v>4.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M34" t="n">
         <v>2.9</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.35</v>
-      </c>
       <c r="N34" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.12</v>
+        <v>4.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.92</v>
+        <v>2.31</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="M35" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="P35" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.18</v>
+        <v>3.98</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="T35" t="n">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.4</v>
+        <v>4.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="O36" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="P36" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.35</v>
+        <v>4.18</v>
       </c>
       <c r="R36" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="T36" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="U36" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W36" t="n">
         <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="M37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O37" t="n">
         <v>5.75</v>
@@ -4839,19 +4839,19 @@
         <v>2.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R37" t="n">
         <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="T37" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="U37" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V37" t="n">
         <v>3.75</v>
@@ -4863,7 +4863,7 @@
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z37" t="n">
         <v>7</v>
@@ -4878,19 +4878,19 @@
         <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AG37" t="n">
         <v>1.11</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
         <v>2.38</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
         <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="U38" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
         <v>5.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.43</v>
+        <v>4.1</v>
       </c>
       <c r="AA38" t="n">
         <v>1.69</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.63</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1412,34 +1412,34 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.33</v>
+        <v>3.31</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>2.52</v>
       </c>
       <c r="O10" t="n">
-        <v>5.67</v>
+        <v>4.61</v>
       </c>
       <c r="P10" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.31</v>
+        <v>3.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="V10" t="n">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.31</v>
+        <v>4.33</v>
       </c>
       <c r="M11" t="n">
-        <v>2.59</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.52</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4.61</v>
+        <v>5.67</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>2.31</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.5</v>
+        <v>4.03</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.46</v>
       </c>
       <c r="S15" t="n">
         <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
         <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
         <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
         <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AG16" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.66</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC20" t="n">
         <v>3.1</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AD20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>2.13</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>3.96</v>
       </c>
       <c r="P21" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.78</v>
+        <v>2.99</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>6.4</v>
+        <v>5.95</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
         <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AG21" t="n">
         <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.39</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.88</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>1.71</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.49</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.02</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.42</v>
+        <v>3.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.25</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.86</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.43</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
         <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O29" t="n">
-        <v>3.18</v>
+        <v>2.79</v>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.48</v>
+        <v>4.62</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V29" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="O30" t="n">
-        <v>3.76</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.07</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.1</v>
+        <v>4.65</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P31" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>2.79</v>
+        <v>3.76</v>
       </c>
       <c r="P34" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.62</v>
+        <v>3.07</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S34" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="T34" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4726,7 +4726,7 @@
         <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="T36" t="n">
         <v>3.64</v>
@@ -4753,19 +4753,19 @@
         <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AD36" t="n">
         <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
         <v>1.23</v>
@@ -4830,10 +4830,10 @@
         <v>5.6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="O37" t="n">
-        <v>5.75</v>
+        <v>4.84</v>
       </c>
       <c r="P37" t="n">
         <v>2.8</v>
@@ -4845,37 +4845,37 @@
         <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="T37" t="n">
         <v>1.92</v>
       </c>
       <c r="U37" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V37" t="n">
         <v>3.75</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z37" t="n">
         <v>7</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AD37" t="n">
         <v>1.97</v>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N39" t="n">
         <v>2.54</v>
@@ -5077,7 +5077,7 @@
         <v>1.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R39" t="n">
         <v>1.48</v>
@@ -5092,7 +5092,7 @@
         <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W39" t="n">
         <v>1.01</v>
@@ -5104,13 +5104,13 @@
         <v>1.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AA39" t="n">
         <v>2.19</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC39" t="n">
         <v>3.9</v>
@@ -5119,10 +5119,10 @@
         <v>1.18</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG39" t="n">
         <v>1.33</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1293,34 +1293,34 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.63</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.31</v>
+        <v>4.33</v>
       </c>
       <c r="M10" t="n">
-        <v>2.59</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.52</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>4.61</v>
+        <v>5.67</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.35</v>
+        <v>2.31</v>
       </c>
       <c r="R10" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.5</v>
+        <v>4.03</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.33</v>
+        <v>3.31</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>2.52</v>
       </c>
       <c r="O11" t="n">
-        <v>5.67</v>
+        <v>4.61</v>
       </c>
       <c r="P11" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.31</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="V11" t="n">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
         <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
         <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.66</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.46</v>
       </c>
       <c r="S16" t="n">
         <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
         <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
         <v>3.9</v>
@@ -2456,22 +2456,22 @@
         <v>2.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
         <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
         <v>5</v>
@@ -2483,7 +2483,7 @@
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
         <v>4.4</v>
@@ -2492,25 +2492,25 @@
         <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD17" t="n">
         <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
         <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46069.5625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.39</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.18</v>
+        <v>1.71</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.49</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.02</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.42</v>
+        <v>3.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>2.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.71</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.449999999999999</v>
+        <v>3.49</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="T22" t="n">
-        <v>2.61</v>
+        <v>3.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>6.15</v>
+        <v>7.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.86</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.6</v>
+        <v>1.42</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
-        <v>2.97</v>
+        <v>2.49</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>4.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.28</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="O24" t="n">
-        <v>4.21</v>
+        <v>2.97</v>
       </c>
       <c r="P24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="T24" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V24" t="n">
-        <v>10</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.49</v>
+        <v>4.21</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.02</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="S25" t="n">
-        <v>3.34</v>
+        <v>2.01</v>
       </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>4.05</v>
       </c>
       <c r="U25" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="V25" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.8</v>
+        <v>2.19</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.52</v>
+        <v>2.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.56</v>
+        <v>5.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.53</v>
+        <v>1.07</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T30" t="n">
         <v>3.2</v>
       </c>
-      <c r="N30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V30" t="n">
+        <v>9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.57</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V30" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AC30" t="n">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="M31" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="N31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.75</v>
       </c>
-      <c r="O31" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.1</v>
+        <v>3.33</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="O32" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="P32" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="V32" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.01</v>
+        <v>2.37</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.33</v>
+        <v>4.65</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>3.76</v>
+        <v>2.79</v>
       </c>
       <c r="P34" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.07</v>
+        <v>4.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U34" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -665,19 +665,19 @@
         <v>4.15</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
         <v>6.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
         <v>2.97</v>
@@ -686,7 +686,7 @@
         <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
         <v>6</v>
@@ -698,34 +698,34 @@
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="AA2" t="n">
         <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46069.22916666666</v>
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.33</v>
+        <v>4.79</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="P10" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="R10" t="n">
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
         <v>1.31</v>
@@ -1647,37 +1647,37 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
         <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AB10" t="n">
         <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.03</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="n">
         <v>2.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
         <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1730,19 +1730,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
-        <v>4.61</v>
+        <v>4.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
         <v>3.35</v>
@@ -1751,10 +1751,10 @@
         <v>1.74</v>
       </c>
       <c r="S11" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="U11" t="n">
         <v>1.15</v>
@@ -1769,31 +1769,31 @@
         <v>1.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD11" t="n">
         <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AF11" t="n">
         <v>1.48</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
         <v>1.26</v>
@@ -1861,22 +1861,22 @@
         <v>2.37</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="T12" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
         <v>8.9</v>
@@ -1888,34 +1888,34 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AA12" t="n">
         <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC12" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2212,31 +2212,31 @@
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
         <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="W15" t="n">
         <v>1.01</v>
@@ -2245,19 +2245,19 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
-        <v>1.71</v>
+        <v>3.92</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.449999999999999</v>
+        <v>2.61</v>
       </c>
       <c r="R20" t="n">
         <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>6.15</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
         <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.43</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC21" t="n">
         <v>3.1</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AD21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.39</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>2.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.49</v>
+        <v>6.47</v>
       </c>
       <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.44</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V22" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.42</v>
+        <v>3.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="O23" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.02</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.25</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22</v>
+        <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="S24" t="n">
-        <v>2.78</v>
+        <v>2.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>2.19</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.97</v>
+        <v>5.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="M25" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>4.21</v>
+        <v>2.49</v>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.01</v>
+        <v>3.34</v>
       </c>
       <c r="T25" t="n">
-        <v>4.05</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.03</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>1.15</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.61</v>
-      </c>
       <c r="Z25" t="n">
-        <v>2.19</v>
+        <v>4.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.83</v>
+        <v>1.52</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.75</v>
+        <v>2.56</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P26" t="n">
         <v>2.4</v>
@@ -3539,13 +3539,13 @@
         <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
         <v>1.68</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="W26" t="n">
         <v>1.15</v>
@@ -3554,28 +3554,28 @@
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
         <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AB26" t="n">
         <v>2.59</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD26" t="n">
         <v>1.71</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AG26" t="n">
         <v>1.23</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.32</v>
+        <v>4.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.31</v>
+        <v>1.49</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="P27" t="n">
         <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.68</v>
+        <v>1.98</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="AA27" t="n">
         <v>1.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>4.68</v>
+        <v>4.32</v>
       </c>
       <c r="N28" t="n">
-        <v>1.49</v>
+        <v>2.31</v>
       </c>
       <c r="O28" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.98</v>
+        <v>2.68</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="AA28" t="n">
         <v>1.37</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.44</v>
+        <v>2.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,28 +3991,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>3.76</v>
+        <v>3.18</v>
       </c>
       <c r="P30" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="R30" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="T30" t="n">
         <v>3.2</v>
@@ -4021,25 +4021,25 @@
         <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC30" t="n">
         <v>4.1</v>
@@ -4048,16 +4048,16 @@
         <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.92</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3.35</v>
+        <v>2.79</v>
       </c>
       <c r="P31" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.12</v>
+        <v>4.62</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="T31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z31" t="n">
         <v>2.75</v>
       </c>
-      <c r="U31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="M33" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="N33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.75</v>
       </c>
-      <c r="O33" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.1</v>
+        <v>3.33</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="O35" t="n">
-        <v>3.14</v>
+        <v>2.96</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.98</v>
+        <v>4.18</v>
       </c>
       <c r="R35" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T35" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="O36" t="n">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="P36" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.18</v>
+        <v>3.98</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T36" t="n">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V36" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
         <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.6</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
-        <v>4.84</v>
+        <v>2.38</v>
       </c>
       <c r="P37" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="U37" t="n">
-        <v>1.92</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.26</v>
+        <v>2.18</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>6.6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>1.36</v>
       </c>
       <c r="O38" t="n">
-        <v>2.38</v>
+        <v>4.84</v>
       </c>
       <c r="P38" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>1.75</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="T38" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="V38" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="W38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.09</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5062,28 +5062,28 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="M39" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P39" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
         <v>3.22</v>
@@ -5092,31 +5092,31 @@
         <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W39" t="n">
         <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y39" t="n">
         <v>1.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
         <v>1.83</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI42"/>
+  <dimension ref="A1:AI41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>6.23</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.7</v>
+        <v>4.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>2.97</v>
+        <v>3.26</v>
       </c>
       <c r="T2" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
         <v>6</v>
@@ -701,7 +701,7 @@
         <v>1.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AA2" t="n">
         <v>1.75</v>
@@ -713,19 +713,19 @@
         <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46069.22916666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1293,34 +1293,34 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1495,10 +1495,10 @@
         <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="O10" t="n">
-        <v>5.68</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>2.33</v>
@@ -1638,7 +1638,7 @@
         <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
         <v>7.7</v>
@@ -1650,25 +1650,25 @@
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
         <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AB10" t="n">
         <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>4.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>1.69</v>
@@ -1677,7 +1677,7 @@
         <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="M11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
         <v>2.37</v>
       </c>
       <c r="O11" t="n">
-        <v>4.56</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
         <v>1.69</v>
@@ -1748,10 +1748,10 @@
         <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="S11" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="T11" t="n">
         <v>4.3</v>
@@ -1766,25 +1766,25 @@
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="Z11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.6</v>
+        <v>6.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
         <v>2.45</v>
@@ -1796,7 +1796,7 @@
         <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1861,16 +1861,16 @@
         <v>2.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
         <v>3.18</v>
@@ -1879,34 +1879,34 @@
         <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>1.66</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q15" t="n">
         <v>4</v>
       </c>
-      <c r="N15" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.31</v>
       </c>
-      <c r="V15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>8.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
         <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>3.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
         <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.66</v>
+        <v>2.48</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
@@ -2471,10 +2471,10 @@
         <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.13</v>
@@ -2483,7 +2483,7 @@
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
         <v>4.4</v>
@@ -2495,22 +2495,22 @@
         <v>2.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46069.5625</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.75</v>
+        <v>3.93</v>
       </c>
       <c r="R18" t="n">
         <v>1.41</v>
@@ -2587,49 +2587,49 @@
         <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
         <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AA18" t="n">
         <v>2.06</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.92</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.61</v>
+        <v>3.49</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>3.18</v>
+        <v>2.49</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.49</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.56</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>2.87</v>
       </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="P22" t="n">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.47</v>
+        <v>3.58</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="T22" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.91</v>
+        <v>3.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.24</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.97</v>
+        <v>3.92</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.05</v>
+        <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="P24" t="n">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.47</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="T24" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.19</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.31</v>
+        <v>3.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.49</v>
+        <v>4.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.02</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="S25" t="n">
-        <v>3.34</v>
+        <v>2.19</v>
       </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>4.05</v>
       </c>
       <c r="U25" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="V25" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.52</v>
+        <v>2.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.56</v>
+        <v>5.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="V30" t="n">
-        <v>8.9</v>
+        <v>6.95</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
         <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.74</v>
+        <v>3.24</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="M31" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="O31" t="n">
-        <v>2.79</v>
+        <v>3.74</v>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.62</v>
+        <v>3.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S31" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T31" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
         <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O32" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S32" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="V32" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AA32" t="n">
         <v>2.37</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V33" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4705,22 +4705,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="O36" t="n">
         <v>3.14</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
         <v>1.53</v>
@@ -4741,37 +4741,37 @@
         <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
         <v>1.41</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC36" t="n">
         <v>4.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AF36" t="n">
         <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.25</v>
+        <v>6.52</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>6.02</v>
       </c>
       <c r="N37" t="n">
-        <v>3.1</v>
+        <v>1.36</v>
       </c>
       <c r="O37" t="n">
-        <v>2.38</v>
+        <v>5.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="V37" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="W37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.09</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.6</v>
+        <v>2.28</v>
       </c>
       <c r="M38" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>1.36</v>
+        <v>2.78</v>
       </c>
       <c r="O38" t="n">
-        <v>4.84</v>
+        <v>2.38</v>
       </c>
       <c r="P38" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>4.9</v>
+        <v>3.04</v>
       </c>
       <c r="T38" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="U38" t="n">
-        <v>1.92</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.26</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.89</v>
+        <v>2.51</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46069.8125</v>
+        <v>46069.875</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5369,125 +5369,6 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46069.875</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>46069</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Portmore United</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="3" t="n">
         <v>46069.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.6</v>
+        <v>2.37</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>1.52</v>
+        <v>2.73</v>
       </c>
       <c r="O8" t="n">
-        <v>5.6</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>1.71</v>
+        <v>4.64</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>2.37</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
         <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.03</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.14</v>
+        <v>1.98</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.74</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>4.64</v>
+        <v>1.71</v>
       </c>
       <c r="O12" t="n">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
         <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.98</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
         <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
         <v>3.35</v>
@@ -2001,28 +2001,28 @@
         <v>9.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AA13" t="n">
         <v>2.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE13" t="n">
         <v>2.2</v>
@@ -2031,10 +2031,10 @@
         <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46069.52083333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>4.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.58</v>
+        <v>5.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.49</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>2.55</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.87</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.58</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.78</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.06</v>
+        <v>1.54</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.49</v>
+        <v>3.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3164,22 +3164,22 @@
         <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="O23" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
         <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="T23" t="n">
         <v>2.55</v>
@@ -3188,28 +3188,28 @@
         <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
         <v>3.78</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AD23" t="n">
         <v>1.35</v>
@@ -3221,10 +3221,10 @@
         <v>2.18</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.74</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="M24" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="P24" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>3.52</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N25" t="n">
         <v>2.75</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.4</v>
-      </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.19</v>
+        <v>3.02</v>
       </c>
       <c r="T25" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.15</v>
+        <v>3.61</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.75</v>
+        <v>2.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>4.68</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>1.49</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="V27" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="M28" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N28" t="n">
-        <v>2.31</v>
+        <v>1.48</v>
       </c>
       <c r="O28" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.68</v>
+        <v>1.98</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.81</v>
+        <v>2.38</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>2.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O32" t="n">
-        <v>6.6</v>
+        <v>3.74</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.28</v>
+        <v>3.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="T32" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
         <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
         <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>3.06</v>
+        <v>2.74</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="R33" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S33" t="n">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V33" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W33" t="n">
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P34" t="n">
         <v>2.05</v>
       </c>
-      <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q34" t="n">
-        <v>4.55</v>
+        <v>2.28</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S34" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="T34" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="U34" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V34" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N35" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T35" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.53</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
-        <v>3.14</v>
+        <v>2.96</v>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.53</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V36" t="n">
-        <v>9</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.41</v>
-      </c>
       <c r="Z36" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -5071,16 +5071,16 @@
         <v>2.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
         <v>2.5</v>
@@ -5089,34 +5089,34 @@
         <v>3.22</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
         <v>1.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" t="n">
         <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC39" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE39" t="n">
         <v>1.83</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -674,13 +674,13 @@
         <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.94</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.26</v>
+        <v>2.97</v>
       </c>
       <c r="T2" t="n">
         <v>2.61</v>
@@ -698,7 +698,7 @@
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
         <v>3.88</v>
@@ -707,13 +707,13 @@
         <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1174,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.37</v>
+        <v>5.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>5.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.74</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.64</v>
+        <v>1.71</v>
       </c>
       <c r="O10" t="n">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>2.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
         <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.98</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>1.71</v>
+        <v>4.64</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>2.37</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
         <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.03</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.14</v>
+        <v>1.98</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>8.35</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
         <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="M16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q16" t="n">
         <v>4</v>
       </c>
-      <c r="N16" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
         <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.48</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2569,16 +2569,16 @@
         <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="P18" t="n">
         <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.93</v>
+        <v>4.99</v>
       </c>
       <c r="R18" t="n">
         <v>1.41</v>
@@ -2590,7 +2590,7 @@
         <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
         <v>7.3</v>
@@ -2599,7 +2599,7 @@
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.28</v>
@@ -2626,7 +2626,7 @@
         <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
         <v>1.97</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="O20" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>2.19</v>
+        <v>3.27</v>
       </c>
       <c r="T20" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>10</v>
+        <v>5.95</v>
       </c>
       <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
         <v>2.6</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.49</v>
+        <v>3.56</v>
       </c>
       <c r="R21" t="n">
         <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
         <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="P22" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>3.52</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.1</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.03</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="Q23" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.55</v>
       </c>
       <c r="U23" t="n">
         <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>5.95</v>
+        <v>5.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
         <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="AD23" t="n">
         <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.18</v>
+        <v>1.54</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.8</v>
+        <v>3.61</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="N25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.75</v>
       </c>
-      <c r="O25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AB25" t="n">
         <v>1.4</v>
       </c>
-      <c r="V25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC25" t="n">
-        <v>2.97</v>
+        <v>5.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,37 +3515,37 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
         <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V26" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="W26" t="n">
         <v>1.15</v>
@@ -3554,34 +3554,34 @@
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
         <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
         <v>1.71</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46069.64583333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P33" t="n">
         <v>2.05</v>
       </c>
-      <c r="M33" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q33" t="n">
-        <v>4.55</v>
+        <v>2.28</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S33" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="T33" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="U33" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V33" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.2</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
-        <v>6.6</v>
+        <v>2.74</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.28</v>
+        <v>4.55</v>
       </c>
       <c r="R34" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="T34" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="U34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.24</v>
       </c>
-      <c r="V34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE34" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.15</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.5</v>
       </c>
-      <c r="R35" t="n">
+      <c r="U35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V35" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.53</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.41</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG35" t="n">
         <v>1.36</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="M36" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T36" t="n">
         <v>3.1</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V36" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
         <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -665,10 +665,10 @@
         <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>6.23</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
@@ -680,7 +680,7 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>2.97</v>
+        <v>3.26</v>
       </c>
       <c r="T2" t="n">
         <v>2.61</v>
@@ -689,7 +689,7 @@
         <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -698,7 +698,7 @@
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
         <v>3.88</v>
@@ -707,10 +707,10 @@
         <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
         <v>1.33</v>
@@ -722,10 +722,10 @@
         <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46069.22916666666</v>
@@ -1260,7 +1260,7 @@
         <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
         <v>3.22</v>
@@ -1281,7 +1281,7 @@
         <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
         <v>8.5</v>
@@ -1293,10 +1293,10 @@
         <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AA7" t="n">
         <v>2.18</v>
@@ -1305,7 +1305,7 @@
         <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" t="n">
         <v>1.18</v>
@@ -1317,7 +1317,7 @@
         <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
         <v>1.44</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>3.23</v>
       </c>
       <c r="M10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA10" t="n">
         <v>3.4</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.03</v>
+        <v>6.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.14</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.23</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.37</v>
       </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.77</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>4.3</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>1.98</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.74</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>4.64</v>
+        <v>1.77</v>
       </c>
       <c r="O12" t="n">
-        <v>2.37</v>
+        <v>5.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.98</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
         <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
         <v>3.35</v>
@@ -2001,7 +2001,7 @@
         <v>9.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.09</v>
@@ -2019,22 +2019,22 @@
         <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
         <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46069.52083333334</v>
@@ -2328,34 +2328,34 @@
         <v>1.99</v>
       </c>
       <c r="M16" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="P16" t="n">
         <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2364,7 +2364,7 @@
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
         <v>3.06</v>
@@ -2373,22 +2373,22 @@
         <v>2.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC16" t="n">
         <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
         <v>1.7</v>
@@ -2450,10 +2450,10 @@
         <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
         <v>2.27</v>
@@ -2468,7 +2468,7 @@
         <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
         <v>1.55</v>
@@ -2486,10 +2486,10 @@
         <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
         <v>2.19</v>
@@ -2498,19 +2498,19 @@
         <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46069.5625</v>
@@ -2572,19 +2572,19 @@
         <v>4.36</v>
       </c>
       <c r="O18" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
         <v>2.94</v>
@@ -2617,7 +2617,7 @@
         <v>3.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
         <v>1.85</v>
@@ -2629,7 +2629,7 @@
         <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
@@ -2819,19 +2819,19 @@
         <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
         <v>3.27</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
         <v>1.07</v>
@@ -2843,13 +2843,13 @@
         <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC20" t="n">
         <v>2.74</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
         <v>2.6</v>
@@ -2935,13 +2935,13 @@
         <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.56</v>
+        <v>3.17</v>
       </c>
       <c r="R21" t="n">
         <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
         <v>3</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="N22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.3</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.52</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="S22" t="n">
-        <v>3.28</v>
+        <v>2.19</v>
       </c>
       <c r="T22" t="n">
-        <v>2.36</v>
+        <v>4.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.59</v>
+        <v>5.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="P23" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>3.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>9.91</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>2.19</v>
+        <v>3.16</v>
       </c>
       <c r="T25" t="n">
-        <v>4.05</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.15</v>
+        <v>3.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.27</v>
+        <v>3.68</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3536,13 +3536,13 @@
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V26" t="n">
         <v>4.33</v>
@@ -3563,7 +3563,7 @@
         <v>1.39</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC26" t="n">
         <v>2.1</v>
@@ -3572,10 +3572,10 @@
         <v>1.71</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AG26" t="n">
         <v>1.55</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>4.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="O27" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="R27" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>2.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1.48</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="V28" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="O30" t="n">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="S30" t="n">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="T30" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="U30" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="V30" t="n">
-        <v>6.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.24</v>
+        <v>2.46</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.7</v>
+        <v>2.27</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T31" t="n">
         <v>3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.2</v>
       </c>
       <c r="U31" t="n">
         <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>2.29</v>
+        <v>2.99</v>
       </c>
       <c r="T33" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="U33" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.46</v>
+        <v>3.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
         <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2.74</v>
+        <v>3.06</v>
       </c>
       <c r="P34" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S34" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="T34" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V34" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4589,13 +4589,13 @@
         <v>2.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N35" t="n">
         <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
         <v>1.93</v>
@@ -4634,16 +4634,16 @@
         <v>2.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
         <v>1.67</v>
@@ -4705,19 +4705,19 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
         <v>3.5</v>
@@ -4726,13 +4726,13 @@
         <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="T36" t="n">
         <v>3.1</v>
       </c>
       <c r="U36" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
         <v>9</v>
@@ -4744,34 +4744,34 @@
         <v>1.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AA36" t="n">
         <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE36" t="n">
         <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG36" t="n">
         <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.52</v>
+        <v>2.28</v>
       </c>
       <c r="M37" t="n">
-        <v>6.02</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>1.36</v>
+        <v>2.78</v>
       </c>
       <c r="O37" t="n">
-        <v>5.75</v>
+        <v>2.38</v>
       </c>
       <c r="P37" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="T37" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="U37" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.65</v>
+        <v>4.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.24</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.89</v>
+        <v>2.51</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.28</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.78</v>
+        <v>1.4</v>
       </c>
       <c r="O38" t="n">
-        <v>2.38</v>
+        <v>5.75</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="S38" t="n">
-        <v>3.04</v>
+        <v>4.9</v>
       </c>
       <c r="T38" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="V38" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.09</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.23</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>1.77</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.04</v>
+        <v>2.77</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.77</v>
       </c>
-      <c r="O12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="S12" t="n">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
-        <v>7.9</v>
+        <v>11.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.73</v>
+        <v>2.04</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.19</v>
+        <v>6.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>8.35</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.48</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>4.21</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>6.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
         <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
         <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,55 +2801,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>9.91</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="T20" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>6.15</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>2.74</v>
@@ -2858,16 +2858,16 @@
         <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>3.68</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2944,7 +2944,7 @@
         <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="U21" t="n">
         <v>1.33</v>
@@ -2962,7 +2962,7 @@
         <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
         <v>2.21</v>
@@ -2971,13 +2971,13 @@
         <v>1.74</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD21" t="n">
         <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AF21" t="n">
         <v>1.84</v>
@@ -3170,22 +3170,22 @@
         <v>2.49</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
         <v>3.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
         <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
         <v>5</v>
@@ -3194,13 +3194,13 @@
         <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
         <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA23" t="n">
         <v>1.65</v>
@@ -3209,10 +3209,10 @@
         <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
         <v>1.53</v>
@@ -3221,7 +3221,7 @@
         <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
         <v>1.75</v>
@@ -3280,25 +3280,25 @@
         <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="O24" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
         <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="T24" t="n">
         <v>2.62</v>
@@ -3316,10 +3316,10 @@
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
         <v>1.85</v>
@@ -3331,13 +3331,13 @@
         <v>2.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG24" t="n">
         <v>1.26</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>9.91</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V25" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="AA25" t="n">
         <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC25" t="n">
         <v>2.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.58</v>
+        <v>2.18</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.68</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
         <v>3.6</v>
@@ -3530,7 +3530,7 @@
         <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.8</v>
+        <v>2.37</v>
       </c>
       <c r="M27" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="V27" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.4</v>
+        <v>5.72</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>4.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="O28" t="n">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="T28" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2.74</v>
+        <v>3.06</v>
       </c>
       <c r="P29" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="T29" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O30" t="n">
-        <v>6.6</v>
+        <v>3.74</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.28</v>
+        <v>3.12</v>
       </c>
       <c r="R30" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="T30" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O31" t="n">
-        <v>3.74</v>
+        <v>6.6</v>
       </c>
       <c r="P31" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.12</v>
+        <v>2.28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S31" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U31" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AG31" t="n">
         <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="P33" t="n">
         <v>2.22</v>
@@ -4369,13 +4369,13 @@
         <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>2.99</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
         <v>2.7</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
         <v>7</v>
@@ -4387,19 +4387,19 @@
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="AA33" t="n">
         <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AD33" t="n">
         <v>1.33</v>
@@ -4411,7 +4411,7 @@
         <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
         <v>1.41</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="T35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U35" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AC35" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AD35" t="n">
         <v>1.15</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG35" t="n">
         <v>1.36</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="P36" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q36" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T36" t="n">
         <v>3.5</v>
       </c>
-      <c r="R36" t="n">
+      <c r="U36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.53</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V36" t="n">
-        <v>9</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.42</v>
-      </c>
       <c r="Z36" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD36" t="n">
         <v>1.15</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
         <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4824,28 +4824,28 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q37" t="n">
         <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="T37" t="n">
         <v>2.44</v>
@@ -4854,22 +4854,22 @@
         <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="W37" t="n">
         <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
         <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB37" t="n">
         <v>2.1</v>
@@ -4887,10 +4887,10 @@
         <v>2.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4982,16 +4982,16 @@
         <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="AA38" t="n">
         <v>1.28</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="AC38" t="n">
         <v>1.89</v>
@@ -5006,10 +5006,10 @@
         <v>2.5</v>
       </c>
       <c r="AG38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>3.4</v>
@@ -5080,7 +5080,7 @@
         <v>3.18</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S39" t="n">
         <v>2.5</v>
@@ -5098,31 +5098,31 @@
         <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
         <v>3.86</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG39" t="n">
         <v>1.33</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="O2" t="n">
         <v>1.92</v>
@@ -674,19 +674,19 @@
         <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.26</v>
+        <v>2.97</v>
       </c>
       <c r="T2" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
         <v>6.25</v>
@@ -701,7 +701,7 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
         <v>1.75</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.37</v>
+        <v>5.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>3.22</v>
+        <v>5.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1412,34 +1412,34 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
         <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
@@ -1659,7 +1659,7 @@
         <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
         <v>3.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.74</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.43</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>4.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.98</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O12" t="n">
         <v>2.37</v>
       </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="U12" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1986,7 +1986,7 @@
         <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
         <v>2.32</v>
@@ -2001,28 +2001,28 @@
         <v>9.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
         <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
         <v>2.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE13" t="n">
         <v>2.2</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.99</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.64</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
         <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
         <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="M16" t="n">
-        <v>4.21</v>
+        <v>3.16</v>
       </c>
       <c r="N16" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2447,7 +2447,7 @@
         <v>1.76</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="N17" t="n">
         <v>3.8</v>
@@ -2462,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
         <v>3.18</v>
@@ -2483,7 +2483,7 @@
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
         <v>4.35</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>9.91</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>3.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>6.15</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.88</v>
+        <v>4.8</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.68</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.17</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="T21" t="n">
-        <v>3.19</v>
+        <v>2.54</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>8.300000000000001</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.19</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.15</v>
+        <v>3.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.75</v>
+        <v>2.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>2.36</v>
+        <v>3.19</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>3.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>3.24</v>
+        <v>5.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.84</v>
+        <v>9.91</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="P24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC24" t="n">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.04</v>
+        <v>1.54</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>3.68</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>3.41</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="S25" t="n">
-        <v>3.27</v>
+        <v>2.02</v>
       </c>
       <c r="T25" t="n">
-        <v>2.56</v>
+        <v>4.05</v>
       </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.05</v>
+        <v>2.19</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.02</v>
+        <v>1.37</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.74</v>
+        <v>5.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3637,31 +3637,31 @@
         <v>2.37</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="S27" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V27" t="n">
         <v>4.3</v>
@@ -3673,10 +3673,10 @@
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.72</v>
+        <v>5.73</v>
       </c>
       <c r="AA27" t="n">
         <v>1.43</v>
@@ -3688,19 +3688,19 @@
         <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3762,7 +3762,7 @@
         <v>1.48</v>
       </c>
       <c r="O28" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="P28" t="n">
         <v>2.62</v>
@@ -3786,7 +3786,7 @@
         <v>3.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
@@ -3810,16 +3810,16 @@
         <v>1.78</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AF28" t="n">
         <v>2.38</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>2.52</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.7</v>
+        <v>4.46</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V29" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AD29" t="n">
         <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O30" t="n">
-        <v>3.74</v>
+        <v>6.2</v>
       </c>
       <c r="P30" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S30" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>2.74</v>
+        <v>3.06</v>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="T32" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.56</v>
+        <v>3.13</v>
       </c>
       <c r="M33" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="O33" t="n">
-        <v>3.12</v>
+        <v>4.1</v>
       </c>
       <c r="P33" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R33" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="T33" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.87</v>
       </c>
-      <c r="AC33" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4592,7 +4592,7 @@
         <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O35" t="n">
         <v>3.22</v>
@@ -4610,13 +4610,13 @@
         <v>2.33</v>
       </c>
       <c r="T35" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
@@ -4631,28 +4631,28 @@
         <v>2.51</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AB35" t="n">
         <v>1.54</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.3</v>
+        <v>4.63</v>
       </c>
       <c r="AD35" t="n">
         <v>1.15</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AF35" t="n">
         <v>1.74</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4708,7 +4708,7 @@
         <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
         <v>3.4</v>
@@ -4759,7 +4759,7 @@
         <v>5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
         <v>2.1</v>
@@ -4836,16 +4836,16 @@
         <v>2.8</v>
       </c>
       <c r="P37" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
         <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="T37" t="n">
         <v>2.44</v>
@@ -4854,19 +4854,19 @@
         <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W37" t="n">
         <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
         <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.95</v>
+        <v>4.42</v>
       </c>
       <c r="AA37" t="n">
         <v>1.69</v>
@@ -4887,10 +4887,10 @@
         <v>2.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4949,7 +4949,7 @@
         <v>5.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O38" t="n">
         <v>5.75</v>
@@ -4967,7 +4967,7 @@
         <v>4.9</v>
       </c>
       <c r="T38" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="U38" t="n">
         <v>1.91</v>
@@ -4985,13 +4985,13 @@
         <v>1.05</v>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AA38" t="n">
         <v>1.28</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AC38" t="n">
         <v>1.89</v>
@@ -5000,10 +5000,10 @@
         <v>1.97</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AG38" t="n">
         <v>3.1</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1174,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1412,34 +1412,34 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>4.64</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>2.37</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.16</v>
+        <v>1.97</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>4.25</v>
+        <v>3.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.74</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.48</v>
-      </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="T12" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V12" t="n">
-        <v>8.9</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>4.21</v>
+        <v>3.16</v>
       </c>
       <c r="N15" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.99</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.99</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.64</v>
-      </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>9.91</v>
       </c>
       <c r="O20" t="n">
-        <v>2.49</v>
+        <v>1.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.52</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="T20" t="n">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>6.15</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>1.54</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>3.68</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>3.17</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.27</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.54</v>
+        <v>3.19</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.05</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>3.19</v>
+        <v>4.05</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="V23" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.95</v>
+        <v>2.19</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.21</v>
+        <v>2.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.9</v>
+        <v>5.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>9.91</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>3.58</v>
       </c>
       <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.3</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.68</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="M25" t="n">
-        <v>2.57</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>2.49</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>4.05</v>
+        <v>2.46</v>
       </c>
       <c r="U25" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.03</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.19</v>
+        <v>4.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.83</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.75</v>
+        <v>2.56</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.49</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.37</v>
+        <v>4.8</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>1.48</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.86</v>
+        <v>2.38</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>2.52</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.8</v>
+        <v>2.37</v>
       </c>
       <c r="M28" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.48</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>3.86</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.65</v>
+        <v>5.73</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.52</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.12</v>
+        <v>3.13</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="O29" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="P29" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.46</v>
+        <v>2.96</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="T29" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD29" t="n">
         <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T30" t="n">
         <v>3.2</v>
       </c>
-      <c r="N30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O32" t="n">
-        <v>3.06</v>
+        <v>6.2</v>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S32" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.46</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="P34" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>4.46</v>
       </c>
       <c r="R34" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.62</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V34" t="n">
-        <v>7</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z34" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="O35" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.5</v>
       </c>
-      <c r="R35" t="n">
+      <c r="U35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V35" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.53</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.42</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.63</v>
+        <v>5</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="O36" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="P36" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V36" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4949,16 +4949,16 @@
         <v>5.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="O38" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R38" t="n">
         <v>1.16</v>
@@ -4985,13 +4985,13 @@
         <v>1.05</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="AA38" t="n">
         <v>1.28</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AC38" t="n">
         <v>1.89</v>
@@ -5000,13 +5000,13 @@
         <v>1.97</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF38" t="n">
         <v>2.59</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.1</v>
+        <v>1.15</v>
       </c>
       <c r="AH38" t="n">
         <v>1.11</v>
@@ -5068,13 +5068,13 @@
         <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O39" t="n">
         <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
         <v>3.18</v>
@@ -5104,16 +5104,16 @@
         <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA39" t="n">
         <v>2.19</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AD39" t="n">
         <v>1.23</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -787,58 +787,58 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG3" t="n">
         <v>1.25</v>
@@ -1382,64 +1382,64 @@
         <v>1.53</v>
       </c>
       <c r="O8" t="n">
-        <v>5.6</v>
+        <v>6.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.64</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.37</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.97</v>
+        <v>1.16</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>4.64</v>
       </c>
       <c r="O11" t="n">
-        <v>5.25</v>
+        <v>2.37</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.16</v>
+        <v>1.97</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>9.91</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="T20" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
         <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.86</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
         <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC20" t="n">
         <v>2.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.68</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.17</v>
+        <v>3.52</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.19</v>
+        <v>2.46</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.9</v>
+        <v>2.56</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>3.17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>3.27</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
-        <v>2.54</v>
+        <v>3.19</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>2.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>9.91</v>
       </c>
       <c r="O25" t="n">
-        <v>2.49</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.52</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="T25" t="n">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>6.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.38</v>
+        <v>1.54</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>3.68</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O30" t="n">
-        <v>3.06</v>
+        <v>6.2</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S30" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4125,7 +4125,7 @@
         <v>1.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R31" t="n">
         <v>1.43</v>
@@ -4170,7 +4170,7 @@
         <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG31" t="n">
         <v>1.37</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>6.2</v>
+        <v>2.82</v>
       </c>
       <c r="P32" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>4.46</v>
       </c>
       <c r="R32" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T32" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U32" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="V32" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
         <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="P34" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.46</v>
+        <v>3.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S34" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T34" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V34" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="O37" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>1.71</v>
       </c>
       <c r="R37" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>3.04</v>
+        <v>4.9</v>
       </c>
       <c r="T37" t="n">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="V37" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y37" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z37" t="n">
-        <v>4.42</v>
+        <v>6.65</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>3.24</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.51</v>
+        <v>1.89</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V38" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.4</v>
       </c>
-      <c r="O38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.6</v>
+        <v>2.37</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>1.53</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
-        <v>6.28</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.4</v>
       </c>
-      <c r="V8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.74</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.48</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="T11" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O12" t="n">
         <v>2.37</v>
       </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.97</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V12" t="n">
-        <v>15</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.99</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.64</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="M16" t="n">
-        <v>4.21</v>
+        <v>3.16</v>
       </c>
       <c r="N16" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.99</v>
+        <v>2.64</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>2.49</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>3.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>9.91</v>
       </c>
       <c r="O21" t="n">
-        <v>2.49</v>
+        <v>1.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.52</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>6.15</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>1.54</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>3.68</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.02</v>
       </c>
       <c r="T22" t="n">
-        <v>3.19</v>
+        <v>4.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.95</v>
+        <v>2.19</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.21</v>
+        <v>2.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.9</v>
+        <v>5.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.9</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V23" t="n">
-        <v>10</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>9.91</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>3.58</v>
       </c>
       <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.3</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.68</v>
+        <v>1.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,22 +3515,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="P26" t="n">
         <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
@@ -3554,10 +3554,10 @@
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="AA26" t="n">
         <v>1.39</v>
@@ -3578,10 +3578,10 @@
         <v>2.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46069.64583333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.8</v>
+        <v>2.37</v>
       </c>
       <c r="M27" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>1.48</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S27" t="n">
-        <v>3.86</v>
+        <v>4.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V27" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.65</v>
+        <v>5.73</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.52</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.37</v>
+        <v>4.8</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>1.48</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.86</v>
+        <v>2.38</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>2.52</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>6.2</v>
+        <v>2.82</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.2</v>
+        <v>4.46</v>
       </c>
       <c r="R30" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S30" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U30" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="V30" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.46</v>
+        <v>1.67</v>
       </c>
       <c r="O31" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="P31" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.14</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="V31" t="n">
-        <v>6.95</v>
+        <v>9.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.24</v>
+        <v>2.49</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.12</v>
+        <v>4.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="O32" t="n">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.46</v>
+        <v>3.14</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.26</v>
       </c>
-      <c r="V32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.42</v>
-      </c>
       <c r="Z32" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.15</v>
+        <v>3.12</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,34 +4467,34 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="O34" t="n">
-        <v>3.06</v>
+        <v>4.1</v>
       </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="R34" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S34" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="T34" t="n">
         <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V34" t="n">
         <v>9</v>
@@ -4503,10 +4503,10 @@
         <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z34" t="n">
         <v>2.74</v>
@@ -4515,25 +4515,25 @@
         <v>2.19</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC34" t="n">
         <v>4.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.4</v>
       </c>
-      <c r="O37" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="O38" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>1.71</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="S38" t="n">
-        <v>3.04</v>
+        <v>4.9</v>
       </c>
       <c r="T38" t="n">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="V38" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y38" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z38" t="n">
-        <v>4.42</v>
+        <v>6.65</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>3.24</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.51</v>
+        <v>1.89</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -668,13 +668,13 @@
         <v>5.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -707,19 +707,19 @@
         <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD2" t="n">
         <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.37</v>
+        <v>5.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>1.53</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>6.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="T10" t="n">
-        <v>3.16</v>
+        <v>4.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.77</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.37</v>
       </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.97</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V11" t="n">
-        <v>15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>4.64</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.37</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.97</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>4.21</v>
+        <v>3.16</v>
       </c>
       <c r="N15" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.99</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.99</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.64</v>
-      </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.52</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="T20" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.17</v>
+        <v>3.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>3.19</v>
+        <v>2.46</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.9</v>
+        <v>2.56</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.05</v>
+        <v>3.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>3.02</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>3.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.12</v>
+        <v>3.13</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="O30" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="P30" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.46</v>
+        <v>2.96</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="T30" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V30" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
         <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD30" t="n">
         <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T31" t="n">
         <v>3.2</v>
       </c>
-      <c r="N31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O33" t="n">
-        <v>3.06</v>
+        <v>6.2</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S33" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.13</v>
+        <v>2.12</v>
       </c>
       <c r="M34" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.26</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="P34" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.96</v>
+        <v>4.46</v>
       </c>
       <c r="R34" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U34" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AD34" t="n">
         <v>1.16</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="O37" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>1.71</v>
       </c>
       <c r="R37" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>3.04</v>
+        <v>4.9</v>
       </c>
       <c r="T37" t="n">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="V37" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y37" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z37" t="n">
-        <v>4.42</v>
+        <v>6.65</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>3.24</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.51</v>
+        <v>1.89</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V38" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.4</v>
       </c>
-      <c r="O38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
         <v>1.27</v>
       </c>
       <c r="V3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.03</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46069.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>4.25</v>
+        <v>3.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.74</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.48</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="T11" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>4.64</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>2.37</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.16</v>
+        <v>1.97</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>3.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="S20" t="n">
-        <v>3.27</v>
+        <v>2.02</v>
       </c>
       <c r="T20" t="n">
-        <v>2.54</v>
+        <v>4.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>2.19</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.02</v>
+        <v>1.37</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.74</v>
+        <v>5.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>9.91</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="P21" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>3.52</v>
       </c>
       <c r="R21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.3</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AH21" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>3.68</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>1.27</v>
       </c>
       <c r="M22" t="n">
-        <v>2.57</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.54</v>
+        <v>9.91</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.41</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>4.05</v>
+        <v>2.61</v>
       </c>
       <c r="U22" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>6.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.19</v>
+        <v>3.86</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.12</v>
       </c>
-      <c r="AE22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>3.68</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.52</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="T23" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AG23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.97</v>
+        <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.17</v>
+        <v>3.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>3.02</v>
       </c>
       <c r="T25" t="n">
-        <v>3.19</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>8.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.9</v>
+        <v>2.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
-        <v>4.1</v>
+        <v>3.06</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.96</v>
+        <v>3.86</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="T30" t="n">
         <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W30" t="n">
         <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA30" t="n">
         <v>2.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="T35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V35" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AC35" t="n">
-        <v>5</v>
+        <v>4.63</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="O36" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="P36" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q36" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T36" t="n">
         <v>3.5</v>
       </c>
-      <c r="R36" t="n">
+      <c r="U36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.53</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.42</v>
-      </c>
       <c r="Z36" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.63</v>
+        <v>5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -665,19 +665,19 @@
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
         <v>2.97</v>
@@ -689,7 +689,7 @@
         <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -698,34 +698,34 @@
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>2.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46069.22916666666</v>
@@ -778,40 +778,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="N3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P3" t="n">
         <v>2</v>
       </c>
-      <c r="O3" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
         <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.03</v>
@@ -820,31 +820,31 @@
         <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46069.3125</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.78</v>
+        <v>2.52</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="O6" t="n">
-        <v>6.15</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="T6" t="n">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>5.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>6.52</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
         <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>4.64</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>2.37</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.16</v>
+        <v>1.97</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.74</v>
+        <v>4.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4.64</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.37</v>
+        <v>5.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.97</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1968,67 +1968,67 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="O13" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="T13" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="U13" t="n">
         <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.42</v>
       </c>
       <c r="AB13" t="n">
         <v>1.44</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
         <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
         <v>1.36</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.99</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.64</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.4</v>
       </c>
-      <c r="M16" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.43</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="T20" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.19</v>
+        <v>3.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.75</v>
+        <v>3.22</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>2.57</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="O21" t="n">
-        <v>2.49</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>2.02</v>
       </c>
       <c r="T21" t="n">
-        <v>2.46</v>
+        <v>4.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.8</v>
+        <v>2.19</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>2.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.56</v>
+        <v>5.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.27</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>9.91</v>
+        <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>2.61</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
         <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="AA22" t="n">
         <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC22" t="n">
         <v>2.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.68</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>2.49</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>3.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3277,25 +3277,25 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>3.56</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
         <v>2.5</v>
@@ -3307,7 +3307,7 @@
         <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
@@ -3316,13 +3316,13 @@
         <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="AB24" t="n">
         <v>1.62</v>
@@ -3331,7 +3331,7 @@
         <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
         <v>1.86</v>
@@ -3340,10 +3340,10 @@
         <v>1.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>5.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>9.91</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="P25" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC25" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.06</v>
+        <v>1.59</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>3.68</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,28 +3515,28 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
         <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="O26" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
         <v>2.09</v>
@@ -3545,22 +3545,22 @@
         <v>1.68</v>
       </c>
       <c r="V26" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.62</v>
+        <v>5.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AB26" t="n">
         <v>2.59</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,55 +3872,55 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.13</v>
+        <v>2.32</v>
       </c>
       <c r="M29" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="T29" t="n">
         <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
         <v>2.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC29" t="n">
         <v>4.05</v>
@@ -3929,16 +3929,16 @@
         <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,28 +3991,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="O30" t="n">
-        <v>3.06</v>
+        <v>3.92</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="T30" t="n">
         <v>3.2</v>
@@ -4021,13 +4021,13 @@
         <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
         <v>1.42</v>
@@ -4036,28 +4036,28 @@
         <v>2.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="M32" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="O32" t="n">
         <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
         <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="AA32" t="n">
         <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE32" t="n">
         <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4467,25 +4467,25 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
         <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="P34" t="n">
         <v>1.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.46</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
         <v>2.34</v>
@@ -4497,7 +4497,7 @@
         <v>1.26</v>
       </c>
       <c r="V34" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
@@ -4506,7 +4506,7 @@
         <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z34" t="n">
         <v>2.62</v>
@@ -4524,16 +4524,16 @@
         <v>1.16</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="M35" t="n">
         <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="P35" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S35" t="n">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U35" t="n">
         <v>1.27</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
         <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.51</v>
+        <v>2.73</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE35" t="n">
         <v>1.98</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O36" t="n">
         <v>2.7</v>
@@ -4720,43 +4720,43 @@
         <v>1.93</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.18</v>
+        <v>4.07</v>
       </c>
       <c r="R36" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="S36" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U36" t="n">
         <v>1.26</v>
       </c>
       <c r="V36" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W36" t="n">
         <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AA36" t="n">
         <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
         <v>1.13</v>
@@ -4768,7 +4768,7 @@
         <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
         <v>1.7</v>
@@ -4824,37 +4824,37 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M37" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O37" t="n">
         <v>5.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O37" t="n">
-        <v>5.6</v>
       </c>
       <c r="P37" t="n">
         <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="T37" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="U37" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V37" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="W37" t="n">
         <v>1.25</v>
@@ -4863,10 +4863,10 @@
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA37" t="n">
         <v>1.28</v>
@@ -4875,16 +4875,16 @@
         <v>3.24</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AE37" t="n">
         <v>1.44</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AG37" t="n">
         <v>1.15</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -1153,43 +1153,43 @@
         <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
         <v>2.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
         <v>1.85</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46069.43402777778</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.74</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.48</v>
-      </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="T10" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>8.9</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.37</v>
       </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.97</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V11" t="n">
-        <v>15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1983,10 +1983,10 @@
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
         <v>2.29</v>
@@ -1995,7 +1995,7 @@
         <v>3.36</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
         <v>8.5</v>
@@ -2010,7 +2010,7 @@
         <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
         <v>2.4</v>
@@ -2022,7 +2022,7 @@
         <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE13" t="n">
         <v>2.2</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46069.53472222222</v>
@@ -2209,22 +2209,22 @@
         <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
         <v>2.69</v>
@@ -2233,10 +2233,10 @@
         <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.01</v>
@@ -2248,13 +2248,13 @@
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
         <v>3.85</v>
@@ -2263,10 +2263,10 @@
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
         <v>1.22</v>
@@ -2331,7 +2331,7 @@
         <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="O16" t="n">
         <v>2.58</v>
@@ -2367,7 +2367,7 @@
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AA16" t="n">
         <v>1.85</v>
@@ -2385,7 +2385,7 @@
         <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
         <v>1.26</v>
@@ -2444,34 +2444,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="P17" t="n">
         <v>2.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>4.41</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
         <v>5.3</v>
@@ -2486,25 +2486,25 @@
         <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
         <v>2.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD17" t="n">
         <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AG17" t="n">
         <v>1.19</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>2.3</v>
@@ -2706,7 +2706,7 @@
         <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>3.07</v>
       </c>
       <c r="U19" t="n">
         <v>1.38</v>
@@ -2715,7 +2715,7 @@
         <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
@@ -2724,13 +2724,13 @@
         <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.37</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
         <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>3.38</v>
@@ -2748,7 +2748,7 @@
         <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="M20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.3</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.51</v>
+        <v>4.08</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="T21" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.19</v>
+        <v>3.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.37</v>
+        <v>1.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.75</v>
+        <v>3.22</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="M22" t="n">
         <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
@@ -3057,43 +3057,43 @@
         <v>2.61</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
         <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
         <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
         <v>2.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
         <v>1.61</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>5.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>9.91</v>
       </c>
       <c r="O23" t="n">
-        <v>2.49</v>
+        <v>1.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.52</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="T23" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>6.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>3.68</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
         <v>2.8</v>
@@ -3292,13 +3292,13 @@
         <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="T24" t="n">
         <v>3.16</v>
@@ -3328,13 +3328,13 @@
         <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AD24" t="n">
         <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
         <v>1.84</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.26</v>
-      </c>
-      <c r="M25" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N25" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>3.68</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,28 +3515,28 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O26" t="n">
         <v>2.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
         <v>2.62</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="T26" t="n">
         <v>2.09</v>
@@ -3545,25 +3545,25 @@
         <v>1.68</v>
       </c>
       <c r="V26" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.45</v>
+        <v>5.62</v>
       </c>
       <c r="AA26" t="n">
         <v>1.46</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AC26" t="n">
         <v>2.1</v>
@@ -3572,13 +3572,13 @@
         <v>1.71</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.37</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>5.22</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>2.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.73</v>
+        <v>6.03</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.86</v>
+        <v>2.53</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.8</v>
+        <v>2.33</v>
       </c>
       <c r="M28" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="N28" t="n">
-        <v>1.48</v>
+        <v>2.43</v>
       </c>
       <c r="O28" t="n">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>3.86</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.65</v>
+        <v>5.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.52</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3884,7 +3884,7 @@
         <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
         <v>3.65</v>
@@ -3920,7 +3920,7 @@
         <v>2.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
         <v>4.05</v>
@@ -3932,7 +3932,7 @@
         <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
         <v>1.28</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.27</v>
+        <v>1.61</v>
       </c>
       <c r="O30" t="n">
-        <v>3.92</v>
+        <v>5.75</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
         <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="O32" t="n">
-        <v>3.6</v>
+        <v>4.01</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="T32" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.39</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N34" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="O34" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.85</v>
       </c>
-      <c r="P34" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.28</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="O35" t="n">
-        <v>3.66</v>
+        <v>2.96</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.6</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3.6</v>
       </c>
-      <c r="O36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.07</v>
-      </c>
       <c r="R36" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="T36" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V36" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4827,16 +4827,16 @@
         <v>7.5</v>
       </c>
       <c r="M37" t="n">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="N37" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="O37" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P37" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q37" t="n">
         <v>1.75</v>
@@ -4845,7 +4845,7 @@
         <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="T37" t="n">
         <v>1.85</v>
@@ -4866,16 +4866,16 @@
         <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AD37" t="n">
         <v>1.91</v>
@@ -4887,7 +4887,7 @@
         <v>2.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AH37" t="n">
         <v>1.11</v>
@@ -4943,28 +4943,28 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="O38" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
         <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="T38" t="n">
         <v>2.44</v>
@@ -4973,25 +4973,25 @@
         <v>1.49</v>
       </c>
       <c r="V38" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="W38" t="n">
         <v>1.09</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
         <v>2.51</v>
@@ -5000,10 +5000,10 @@
         <v>1.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG38" t="n">
         <v>1.29</v>
@@ -5062,40 +5062,40 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q39" t="n">
         <v>3.18</v>
       </c>
       <c r="R39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
         <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
         <v>1.02</v>
@@ -5104,28 +5104,28 @@
         <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH39" t="n">
         <v>1.36</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6.52</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1498,22 +1498,22 @@
         <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="O9" t="n">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>4.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="T9" t="n">
         <v>3.2</v>
@@ -1522,43 +1522,43 @@
         <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46069.43402777778</v>
@@ -1849,31 +1849,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.7</v>
+        <v>4.19</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>5.41</v>
+        <v>5.19</v>
       </c>
       <c r="P12" t="n">
         <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
         <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
         <v>1.3</v>
@@ -1888,19 +1888,19 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
         <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
@@ -1909,13 +1909,13 @@
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>4.16</v>
       </c>
       <c r="O14" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="T14" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.98</v>
+        <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46069.53472222222</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>6.5</v>
+        <v>3.66</v>
       </c>
       <c r="O15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.66</v>
+        <v>8.69</v>
       </c>
       <c r="O16" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
         <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>6.44</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.6</v>
+        <v>4.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
         <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA18" t="n">
         <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="AD18" t="n">
         <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.53</v>
+        <v>1.98</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>6.44</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.85</v>
+        <v>7.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
-        <v>3.07</v>
+        <v>2.91</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
         <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AD19" t="n">
         <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.08</v>
+        <v>3.63</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>3.16</v>
       </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.46</v>
+        <v>2.78</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.56</v>
+        <v>3.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.27</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z22" t="n">
         <v>4</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AA22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.18</v>
+        <v>1.59</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.7</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>3.09</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.26</v>
-      </c>
-      <c r="M23" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.68</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.59</v>
+        <v>2.61</v>
       </c>
       <c r="R24" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>2.59</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="M25" t="n">
-        <v>2.57</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.41</v>
+        <v>4.08</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>4.05</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.03</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.19</v>
+        <v>4.46</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.83</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.75</v>
+        <v>2.56</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>1.61</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.65</v>
+        <v>2.29</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V29" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>2.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>5.75</v>
+        <v>3.09</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.29</v>
+        <v>3.05</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="T30" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U30" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.49</v>
+        <v>3.12</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S34" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T34" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
         <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AG34" t="n">
         <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="N35" t="n">
-        <v>3.35</v>
+        <v>2.39</v>
       </c>
       <c r="O35" t="n">
-        <v>2.96</v>
+        <v>3.86</v>
       </c>
       <c r="P35" t="n">
         <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.07</v>
+        <v>3.02</v>
       </c>
       <c r="R35" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="T35" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.55</v>
+        <v>4.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="M36" t="n">
         <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="O36" t="n">
-        <v>3.66</v>
+        <v>2.71</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T36" t="n">
         <v>3.6</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W36" t="n">
         <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.73</v>
+        <v>2.57</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.5</v>
+        <v>6.45</v>
       </c>
       <c r="M37" t="n">
-        <v>5.75</v>
+        <v>6.06</v>
       </c>
       <c r="N37" t="n">
         <v>1.35</v>
@@ -4845,19 +4845,19 @@
         <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T37" t="n">
         <v>1.85</v>
       </c>
       <c r="U37" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="V37" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46069.89583333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
@@ -683,10 +683,10 @@
         <v>2.97</v>
       </c>
       <c r="T2" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V2" t="n">
         <v>6</v>
@@ -698,22 +698,22 @@
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8</v>
@@ -722,7 +722,7 @@
         <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
         <v>2.52</v>
@@ -778,31 +778,31 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="O3" t="n">
-        <v>4.05</v>
+        <v>4.24</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
         <v>1.26</v>
@@ -811,7 +811,7 @@
         <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
         <v>1.03</v>
@@ -823,22 +823,22 @@
         <v>2.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
         <v>1.3</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.54</v>
+        <v>5.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>1.58</v>
       </c>
       <c r="O6" t="n">
-        <v>3.18</v>
+        <v>6.46</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AD6" t="n">
         <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6.52</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>4.38</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="T10" t="n">
-        <v>4.25</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.64</v>
+        <v>5.42</v>
       </c>
       <c r="O11" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6.02</v>
       </c>
       <c r="R11" t="n">
         <v>1.48</v>
@@ -1754,7 +1754,7 @@
         <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
         <v>1.28</v>
@@ -1769,34 +1769,34 @@
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
         <v>2.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.19</v>
+        <v>3.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="O12" t="n">
-        <v>5.19</v>
+        <v>4.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.51</v>
+        <v>3.32</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.23</v>
+        <v>3.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1971,16 +1971,16 @@
         <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
         <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
         <v>4.8</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
         <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="O15" t="n">
         <v>2.58</v>
@@ -2224,10 +2224,10 @@
         <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
         <v>2.96</v>
@@ -2236,16 +2236,16 @@
         <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
         <v>2.95</v>
@@ -2257,7 +2257,7 @@
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
@@ -2266,7 +2266,7 @@
         <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
         <v>1.26</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="O17" t="n">
         <v>2.35</v>
@@ -2462,10 +2462,10 @@
         <v>4.41</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
         <v>2.36</v>
@@ -2474,7 +2474,7 @@
         <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.13</v>
@@ -2489,7 +2489,7 @@
         <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
         <v>2.19</v>
@@ -2498,7 +2498,7 @@
         <v>2.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
         <v>1.55</v>
@@ -2507,10 +2507,10 @@
         <v>2.27</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46069.5625</v>
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>6.44</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
         <v>7.3</v>
@@ -2721,34 +2721,34 @@
         <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>4.72</v>
       </c>
       <c r="P20" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.63</v>
+        <v>3.32</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>2.59</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>3.16</v>
+        <v>4.05</v>
       </c>
       <c r="U20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V20" t="n">
+        <v>13</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.46</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
         <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.46</v>
+        <v>3.63</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>3.02</v>
+        <v>2.59</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="U21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.4</v>
       </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z21" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="n">
         <v>8.5</v>
@@ -3051,7 +3051,7 @@
         <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="Q22" t="n">
         <v>7.5</v>
@@ -3090,7 +3090,7 @@
         <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AD22" t="n">
         <v>1.4</v>
@@ -3099,13 +3099,13 @@
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG22" t="n">
         <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.09</v>
+        <v>3.68</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="T23" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.19</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.37</v>
+        <v>1.88</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.75</v>
+        <v>3.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.27</v>
+        <v>1.93</v>
       </c>
       <c r="M24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q24" t="n">
         <v>3.4</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.61</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.91</v>
+        <v>3.34</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.08</v>
+        <v>2.68</v>
       </c>
       <c r="R25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.25</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z25" t="n">
-        <v>4.46</v>
+        <v>3.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,19 +3515,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="O26" t="n">
         <v>2.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q26" t="n">
         <v>2.62</v>
@@ -3554,16 +3554,16 @@
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.62</v>
+        <v>5.45</v>
       </c>
       <c r="AA26" t="n">
         <v>1.46</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC26" t="n">
         <v>2.1</v>
@@ -3572,13 +3572,13 @@
         <v>1.71</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>2.33</v>
       </c>
       <c r="M27" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O27" t="n">
-        <v>5.22</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S27" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.03</v>
+        <v>5.9</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF27" t="n">
-        <v>2.53</v>
+        <v>2.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.33</v>
+        <v>5.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.43</v>
+        <v>1.49</v>
       </c>
       <c r="O28" t="n">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="R28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.16</v>
       </c>
-      <c r="S28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>4.01</v>
+        <v>2.85</v>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE32" t="n">
         <v>1.93</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="M33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="T33" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V33" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4952,22 +4952,22 @@
         <v>3.06</v>
       </c>
       <c r="O38" t="n">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="P38" t="n">
         <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>3.21</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T38" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U38" t="n">
         <v>1.49</v>
@@ -4997,7 +4997,7 @@
         <v>2.51</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE38" t="n">
         <v>1.6</v>
@@ -5006,10 +5006,10 @@
         <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5062,16 +5062,16 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.62</v>
+        <v>3.01</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O39" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P39" t="n">
         <v>1.92</v>
@@ -5083,13 +5083,13 @@
         <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T39" t="n">
         <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V39" t="n">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z39" t="n">
         <v>2.9</v>
@@ -5122,13 +5122,13 @@
         <v>1.83</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46069.71875</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.38</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>4.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.45</v>
+        <v>3.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="S10" t="n">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.21</v>
+        <v>3.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.88</v>
+        <v>5.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.25</v>
+        <v>4.38</v>
       </c>
       <c r="M12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.7</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V12" t="n">
-        <v>15</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AA12" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.6</v>
+        <v>3.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.95</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
         <v>7.3</v>
       </c>
       <c r="W18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.03</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.98</v>
+        <v>2.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>4.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
         <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="O20" t="n">
-        <v>4.72</v>
+        <v>1.7</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.32</v>
+        <v>7.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>3.16</v>
       </c>
       <c r="T20" t="n">
-        <v>4.05</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>6.15</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>3.68</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.8</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.16</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.86</v>
+        <v>3.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.27</v>
+        <v>3.34</v>
       </c>
       <c r="M22" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.5</v>
+        <v>2.68</v>
       </c>
       <c r="R22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>3.68</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
         <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.46</v>
+        <v>3.63</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>3.02</v>
+        <v>2.59</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.4</v>
       </c>
-      <c r="V23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.45</v>
+        <v>4.72</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="S24" t="n">
-        <v>3.28</v>
+        <v>2.04</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>4.05</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.46</v>
+        <v>2.19</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.66</v>
+        <v>2.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.59</v>
+        <v>5.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.07</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.34</v>
+        <v>1.93</v>
       </c>
       <c r="M25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.4</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.68</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.33</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.43</v>
+        <v>1.49</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.16</v>
       </c>
-      <c r="S27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.5</v>
+        <v>2.33</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="N28" t="n">
-        <v>1.49</v>
+        <v>2.43</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.03</v>
+        <v>5.9</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB28" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF28" t="n">
-        <v>2.53</v>
+        <v>2.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>2.41</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N31" t="n">
-        <v>1.61</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.29</v>
+        <v>3.45</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S31" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="T31" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U31" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="V31" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="T32" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="U32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V32" t="n">
+        <v>7</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.26</v>
       </c>
-      <c r="V32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE32" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.32</v>
+        <v>5</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>1.61</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="P34" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.65</v>
+        <v>2.29</v>
       </c>
       <c r="R34" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V34" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>3.86</v>
+        <v>2.71</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.02</v>
+        <v>4.07</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S35" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U35" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.71</v>
+        <v>4.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.69</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.37</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="N36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T36" t="n">
         <v>3.2</v>
       </c>
-      <c r="O36" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V36" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
         <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.55</v>
+        <v>4.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
         <v>3.77</v>
@@ -5345,13 +5345,13 @@
         <v>2.74</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.37</v>
+        <v>2.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AD41" t="n">
         <v>1.17</v>
@@ -5363,7 +5363,7 @@
         <v>1.81</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AH41" t="n">
         <v>1.32</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>4.38</v>
       </c>
       <c r="M10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.7</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V10" t="n">
-        <v>15</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AA10" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.6</v>
+        <v>3.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.69</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.93</v>
-      </c>
       <c r="Q11" t="n">
-        <v>6.02</v>
+        <v>3.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V11" t="n">
+        <v>15</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.28</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC11" t="n">
-        <v>4.24</v>
+        <v>5.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.99</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.38</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.78</v>
+        <v>5.42</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>6.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.88</v>
+        <v>4.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.99</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>4.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
         <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.95</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
         <v>7.3</v>
       </c>
       <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.03</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>2.47</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.4</v>
+        <v>2.75</v>
       </c>
       <c r="N20" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>4.72</v>
       </c>
       <c r="P20" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.5</v>
+        <v>3.32</v>
       </c>
       <c r="R20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V20" t="n">
+        <v>13</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.68</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>3.34</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
         <v>1.05</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.34</v>
+        <v>2.58</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.68</v>
+        <v>3.63</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>2.59</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>3.16</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>5.95</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.7</v>
+        <v>2.78</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2.59</v>
+        <v>3.28</v>
       </c>
       <c r="T23" t="n">
-        <v>3.16</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.78</v>
+        <v>4.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.86</v>
+        <v>2.59</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.72</v>
+        <v>1.7</v>
       </c>
       <c r="P24" t="n">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.32</v>
+        <v>7.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.04</v>
+        <v>3.16</v>
       </c>
       <c r="T24" t="n">
-        <v>4.05</v>
+        <v>2.54</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>6.15</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>3.68</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.59</v>
+        <v>3.33</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3521,67 +3521,67 @@
         <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="O26" t="n">
         <v>2.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V26" t="n">
         <v>4.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.45</v>
+        <v>5.66</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46069.64583333334</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N27" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
         <v>5</v>
@@ -3655,10 +3655,10 @@
         <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="U27" t="n">
         <v>1.72</v>
@@ -3676,7 +3676,7 @@
         <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.03</v>
+        <v>6.12</v>
       </c>
       <c r="AA27" t="n">
         <v>1.37</v>
@@ -3691,10 +3691,10 @@
         <v>1.73</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AG27" t="n">
         <v>1.16</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="M28" t="n">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="N28" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O28" t="n">
         <v>2.8</v>
@@ -3771,22 +3771,22 @@
         <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
         <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
         <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
@@ -3795,19 +3795,19 @@
         <v>1.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
         <v>1.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AC28" t="n">
         <v>2.09</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE28" t="n">
         <v>1.37</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.85</v>
-      </c>
       <c r="P29" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T29" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="U29" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
         <v>1.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="M31" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF31" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG31" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
         <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="O32" t="n">
-        <v>3.09</v>
+        <v>3.65</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="T32" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.28</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="P33" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="O34" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="N35" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.2</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V35" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.55</v>
+        <v>4.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="M36" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="O36" t="n">
-        <v>3.86</v>
+        <v>2.71</v>
       </c>
       <c r="P36" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.02</v>
+        <v>4.07</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S36" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="T36" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W36" t="n">
         <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.71</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.69</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.37</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.45</v>
+        <v>2.29</v>
       </c>
       <c r="M37" t="n">
-        <v>6.06</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>1.35</v>
+        <v>3.06</v>
       </c>
       <c r="O37" t="n">
-        <v>5.25</v>
+        <v>2.82</v>
       </c>
       <c r="P37" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.75</v>
+        <v>3.21</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>4.4</v>
+        <v>3.04</v>
       </c>
       <c r="T37" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>3.72</v>
+        <v>5.8</v>
       </c>
       <c r="W37" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>4.46</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.76</v>
+        <v>2.51</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.29</v>
+        <v>6.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>6.06</v>
       </c>
       <c r="N38" t="n">
-        <v>3.06</v>
+        <v>1.35</v>
       </c>
       <c r="O38" t="n">
-        <v>2.82</v>
+        <v>5.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.21</v>
+        <v>1.75</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="V38" t="n">
-        <v>5.8</v>
+        <v>3.72</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.46</v>
+        <v>7</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.51</v>
+        <v>1.76</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5300,16 +5300,16 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="O41" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="P41" t="n">
         <v>1.95</v>
@@ -5351,7 +5351,7 @@
         <v>1.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="AD41" t="n">
         <v>1.17</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>5.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>6.46</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
         <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.64</v>
       </c>
-      <c r="AC7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.38</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>4.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.45</v>
+        <v>3.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="S10" t="n">
-        <v>2.53</v>
+        <v>1.99</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.21</v>
+        <v>3.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.88</v>
+        <v>5.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.25</v>
+        <v>4.38</v>
       </c>
       <c r="M11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.7</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V11" t="n">
-        <v>15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AA11" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.6</v>
+        <v>3.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1852,22 +1852,22 @@
         <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="N12" t="n">
-        <v>5.42</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.02</v>
+        <v>4.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
         <v>2.38</v>
@@ -1897,25 +1897,25 @@
         <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="AD12" t="n">
         <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.58</v>
+        <v>8.69</v>
       </c>
       <c r="O15" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
         <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>4</v>
       </c>
-      <c r="N16" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
         <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.02</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>2.35</v>
       </c>
       <c r="P17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.41</v>
+        <v>4.25</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
@@ -2474,7 +2474,7 @@
         <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
         <v>1.13</v>
@@ -2489,7 +2489,7 @@
         <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
         <v>2.19</v>
@@ -2498,16 +2498,16 @@
         <v>2.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
         <v>1.84</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.95</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
         <v>7.3</v>
       </c>
       <c r="W18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.03</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.98</v>
+        <v>2.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>4.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
         <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,70 +2801,70 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="M20" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O20" t="n">
-        <v>4.72</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.32</v>
+        <v>2.68</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>5.95</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.19</v>
+        <v>3.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
         <v>1.3</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.58</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>3.69</v>
       </c>
       <c r="O22" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.16</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>5.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="T23" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>6.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.46</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.59</v>
+        <v>2.92</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>3.68</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.27</v>
       </c>
-      <c r="M24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.92</v>
+        <v>4.32</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.68</v>
+        <v>1.46</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V25" t="n">
+        <v>13</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2.25</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AF25" t="n">
-        <v>2.03</v>
+        <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="M27" t="n">
-        <v>4.7</v>
+        <v>4.42</v>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.12</v>
+        <v>5.75</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF27" t="n">
-        <v>2.47</v>
+        <v>2.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.42</v>
+        <v>4.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U28" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>6.12</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.86</v>
+        <v>2.47</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>3.8</v>
       </c>
       <c r="M29" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="M31" t="n">
         <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="O31" t="n">
-        <v>3.09</v>
+        <v>3.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S31" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="T31" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.28</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N32" t="n">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
@@ -4268,34 +4268,34 @@
         <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.29</v>
+        <v>6.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>6.06</v>
       </c>
       <c r="N37" t="n">
-        <v>3.06</v>
+        <v>1.35</v>
       </c>
       <c r="O37" t="n">
-        <v>2.82</v>
+        <v>5.25</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.21</v>
+        <v>1.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="V37" t="n">
-        <v>5.8</v>
+        <v>3.72</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.46</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.51</v>
+        <v>1.76</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.45</v>
+        <v>2.29</v>
       </c>
       <c r="M38" t="n">
-        <v>6.06</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>1.35</v>
+        <v>3.06</v>
       </c>
       <c r="O38" t="n">
-        <v>5.25</v>
+        <v>2.82</v>
       </c>
       <c r="P38" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.75</v>
+        <v>3.21</v>
       </c>
       <c r="R38" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>4.4</v>
+        <v>3.04</v>
       </c>
       <c r="T38" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="U38" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
-        <v>3.72</v>
+        <v>5.8</v>
       </c>
       <c r="W38" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>4.46</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.76</v>
+        <v>2.51</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5300,34 +5300,34 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3.62</v>
+        <v>4.24</v>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S41" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="T41" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="U41" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="V41" t="n">
         <v>8.699999999999999</v>
@@ -5339,34 +5339,34 @@
         <v>1.06</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.98</v>
+        <v>4.35</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46069.89583333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="M2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.95</v>
@@ -677,19 +677,19 @@
         <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
         <v>2.97</v>
       </c>
       <c r="T2" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -707,25 +707,25 @@
         <v>1.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
         <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46069.22916666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="N3" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="O3" t="n">
         <v>4.24</v>
@@ -796,10 +796,10 @@
         <v>2.97</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
         <v>3.28</v>
@@ -835,10 +835,10 @@
         <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
         <v>1.3</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46069.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.58</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>6.46</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
         <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1492,55 +1492,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N9" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="O9" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
         <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
         <v>2.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>4.1</v>
@@ -1555,10 +1555,10 @@
         <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46069.43402777778</v>
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.38</v>
+        <v>4.54</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="O11" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="P11" t="n">
         <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
         <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="U11" t="n">
         <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -1769,7 +1769,7 @@
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
         <v>2.7</v>
@@ -1778,13 +1778,13 @@
         <v>2.21</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC11" t="n">
         <v>3.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -1793,7 +1793,7 @@
         <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
         <v>1.18</v>
@@ -1968,40 +1968,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
         <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
         <v>3.36</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
         <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.07</v>
@@ -2013,7 +2013,7 @@
         <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB13" t="n">
         <v>1.44</v>
@@ -2022,13 +2022,13 @@
         <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
         <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
         <v>1.36</v>
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.16</v>
+        <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.75</v>
+        <v>5.54</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
         <v>3.28</v>
@@ -2117,43 +2117,43 @@
         <v>1.26</v>
       </c>
       <c r="V14" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="W14" t="n">
         <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="AA14" t="n">
         <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46069.53472222222</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
         <v>4</v>
       </c>
-      <c r="N15" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
         <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.95</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.58</v>
-      </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
         <v>2.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.25</v>
+        <v>4.36</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
@@ -2468,10 +2468,10 @@
         <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
         <v>5</v>
@@ -2498,7 +2498,7 @@
         <v>2.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
         <v>1.54</v>
@@ -2510,7 +2510,7 @@
         <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46069.5625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>4.19</v>
       </c>
       <c r="O18" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="T18" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.95</v>
+        <v>6.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="T19" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
         <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
         <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>4.72</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.68</v>
+        <v>3.36</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="V20" t="n">
-        <v>5.95</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.07</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>2.13</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="M22" t="n">
         <v>3.5</v>
@@ -3048,34 +3048,34 @@
         <v>3.69</v>
       </c>
       <c r="O22" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T22" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="W22" t="n">
         <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
         <v>1.2</v>
@@ -3096,10 +3096,10 @@
         <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG22" t="n">
         <v>1.25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>8.5</v>
+        <v>2.85</v>
       </c>
       <c r="O23" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>3.16</v>
+        <v>2.74</v>
       </c>
       <c r="T23" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>3.61</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.68</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>2.7</v>
+        <v>5.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>4.72</v>
+        <v>1.68</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.36</v>
+        <v>8.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>2.04</v>
+        <v>3.16</v>
       </c>
       <c r="T25" t="n">
-        <v>4.05</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="V25" t="n">
-        <v>13</v>
+        <v>6.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.19</v>
+        <v>3.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AE25" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>3.78</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>4.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V27" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.12</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB28" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF28" t="n">
-        <v>2.47</v>
+        <v>2.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>5.75</v>
+        <v>4.95</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.29</v>
+        <v>2.72</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S30" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="T30" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U30" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.27</v>
+        <v>3.41</v>
       </c>
       <c r="O31" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="R31" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U31" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S32" t="n">
         <v>2.41</v>
       </c>
-      <c r="M32" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.36</v>
-      </c>
       <c r="T32" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
@@ -4268,34 +4268,34 @@
         <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="M33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="T33" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="U33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.26</v>
       </c>
-      <c r="V33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE33" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.96</v>
+        <v>4.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="T34" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="Z34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC34" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AD34" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.73</v>
+        <v>2.29</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.37</v>
+        <v>2.11</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.37</v>
+        <v>1.07</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2.39</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.02</v>
+        <v>3.94</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S35" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="U35" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.71</v>
+        <v>4.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N36" t="n">
-        <v>3.2</v>
+        <v>2.31</v>
       </c>
       <c r="O36" t="n">
-        <v>2.71</v>
+        <v>3.32</v>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.07</v>
+        <v>3.16</v>
       </c>
       <c r="R36" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="T36" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V36" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
         <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.55</v>
+        <v>4.73</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.45</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>6.06</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>1.35</v>
+        <v>2.96</v>
       </c>
       <c r="O37" t="n">
-        <v>5.25</v>
+        <v>2.65</v>
       </c>
       <c r="P37" t="n">
-        <v>2.85</v>
+        <v>2.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.75</v>
+        <v>3.58</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="T37" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>3.72</v>
+        <v>5.8</v>
       </c>
       <c r="W37" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>3.92</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.76</v>
+        <v>2.54</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.29</v>
+        <v>7.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>6.05</v>
       </c>
       <c r="N38" t="n">
-        <v>3.06</v>
+        <v>1.38</v>
       </c>
       <c r="O38" t="n">
-        <v>2.82</v>
+        <v>6.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.21</v>
+        <v>1.77</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>3.04</v>
+        <v>4.6</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="V38" t="n">
-        <v>5.8</v>
+        <v>3.62</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.46</v>
+        <v>7</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.51</v>
+        <v>1.74</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.23</v>
+        <v>2.99</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
         <v>3.65</v>
       </c>
       <c r="P39" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W39" t="n">
         <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="AD39" t="n">
         <v>1.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46069.71875</v>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,194 +5181,75 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46069.875</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>46069</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Portmore United</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>3</v>
-      </c>
-      <c r="M41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O41" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V41" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI41" s="3" t="n">
         <v>46069.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -781,7 +781,7 @@
         <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
         <v>2.21</v>
@@ -799,7 +799,7 @@
         <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
         <v>3.28</v>
@@ -829,10 +829,10 @@
         <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
         <v>1.91</v>
@@ -900,31 +900,31 @@
         <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="P4" t="n">
         <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.29</v>
+        <v>4.51</v>
       </c>
       <c r="R4" t="n">
         <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
         <v>8.5</v>
@@ -936,34 +936,34 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
         <v>2.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
         <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD4" t="n">
         <v>1.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG4" t="n">
         <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46069.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>6.45</v>
+        <v>3.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.32</v>
       </c>
-      <c r="V6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z6" t="n">
-        <v>2.96</v>
+        <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>5.86</v>
       </c>
       <c r="M7" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>6.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.13</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.02</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1495,13 +1495,13 @@
         <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
         <v>1.85</v>
@@ -1534,7 +1534,7 @@
         <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AA9" t="n">
         <v>2.35</v>
@@ -1543,16 +1543,16 @@
         <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD9" t="n">
         <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
         <v>1.31</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>4.54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="O10" t="n">
-        <v>4.15</v>
+        <v>5.19</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>1.99</v>
+        <v>2.54</v>
       </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.43</v>
+        <v>2.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.6</v>
+        <v>3.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.54</v>
+        <v>1.69</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="n">
-        <v>1.81</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>5.19</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>4.72</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>4.15</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.72</v>
+        <v>3.32</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V12" t="n">
+        <v>15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.28</v>
       </c>
-      <c r="V12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AC12" t="n">
-        <v>4.25</v>
+        <v>5.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.98</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.54</v>
+        <v>5.81</v>
       </c>
       <c r="R14" t="n">
         <v>1.48</v>
@@ -2126,34 +2126,34 @@
         <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AA14" t="n">
         <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46069.53472222222</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.95</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
         <v>2.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>3.58</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.02</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
         <v>2.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.19</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>6.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>4.19</v>
       </c>
       <c r="O19" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q19" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
-        <v>2.7</v>
+        <v>5.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>4.72</v>
+        <v>1.68</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.36</v>
+        <v>8.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>3.16</v>
       </c>
       <c r="T20" t="n">
-        <v>4.05</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>6.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.19</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AE20" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>3.78</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.13</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.59</v>
+        <v>3.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V21" t="n">
-        <v>5.95</v>
+        <v>6.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>4.72</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="S23" t="n">
-        <v>2.74</v>
+        <v>2.04</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="U23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V23" t="n">
+        <v>13</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.39</v>
       </c>
-      <c r="V23" t="n">
-        <v>7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3277,25 +3277,25 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
         <v>2.6</v>
@@ -3307,19 +3307,19 @@
         <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
         <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA24" t="n">
         <v>2.2</v>
@@ -3328,22 +3328,22 @@
         <v>1.64</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.32</v>
+        <v>3.1</v>
       </c>
       <c r="AD24" t="n">
         <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG24" t="n">
         <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.15</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>9.220000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="O25" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.5</v>
+        <v>2.59</v>
       </c>
       <c r="R25" t="n">
         <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AA25" t="n">
         <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.78</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="O29" t="n">
-        <v>3.16</v>
+        <v>2.48</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T29" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.9</v>
+        <v>5.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="O30" t="n">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.72</v>
+        <v>2.21</v>
       </c>
       <c r="R30" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="T30" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>2.11</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="M31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="N31" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S31" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="T31" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V31" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.59</v>
+        <v>2.86</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="O32" t="n">
-        <v>3.65</v>
+        <v>3.16</v>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
@@ -4268,34 +4268,34 @@
         <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AB32" t="n">
         <v>1.61</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
         <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="P34" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.24</v>
+        <v>2.72</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S34" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U34" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,99 +871,99 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46069.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46069.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="M6" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>4.04</v>
       </c>
       <c r="O6" t="n">
-        <v>3.22</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="T7" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE7" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>2.44</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>4.04</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.65</v>
+        <v>3.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.54</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>5.19</v>
+        <v>4.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="S10" t="n">
-        <v>2.54</v>
+        <v>1.99</v>
       </c>
       <c r="T10" t="n">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.21</v>
+        <v>3.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.88</v>
+        <v>5.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.1</v>
+        <v>4.22</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="O12" t="n">
-        <v>4.15</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.32</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.43</v>
+        <v>2.27</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1971,28 +1971,28 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
         <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
         <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="R13" t="n">
         <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="T13" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="U13" t="n">
         <v>1.27</v>
@@ -2004,10 +2004,10 @@
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
         <v>2.4</v>
@@ -2016,10 +2016,10 @@
         <v>2.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
         <v>1.15</v>
@@ -2331,16 +2331,16 @@
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="P16" t="n">
         <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
@@ -2355,7 +2355,7 @@
         <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2367,10 +2367,10 @@
         <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
@@ -2391,7 +2391,7 @@
         <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2444,34 +2444,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="O17" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="P17" t="n">
         <v>2.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
         <v>5</v>
@@ -2486,25 +2486,25 @@
         <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
         <v>1.21</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.99</v>
       </c>
       <c r="M18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N18" t="n">
         <v>4</v>
       </c>
-      <c r="N18" t="n">
-        <v>7</v>
-      </c>
       <c r="O18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.04</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="AG18" t="n">
         <v>1.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.19</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.85</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
         <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
         <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.15</v>
+        <v>2.7</v>
       </c>
       <c r="N20" t="n">
-        <v>9.220000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.68</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q20" t="n">
-        <v>8.5</v>
+        <v>3.36</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>3.16</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="V20" t="n">
-        <v>6.05</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.24</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.78</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="M21" t="n">
         <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.89</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.66</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="T21" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
         <v>1.05</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
         <v>3.69</v>
       </c>
       <c r="O22" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
@@ -3063,7 +3063,7 @@
         <v>3.34</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
         <v>1.53</v>
@@ -3075,19 +3075,19 @@
         <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
         <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>4.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
         <v>2.53</v>
@@ -3096,10 +3096,10 @@
         <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
         <v>1.25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="O23" t="n">
-        <v>4.72</v>
+        <v>2.95</v>
       </c>
       <c r="P23" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="R23" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.04</v>
       </c>
-      <c r="T23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V23" t="n">
-        <v>13</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>5.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.13</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.59</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
         <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>6.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AA25" t="n">
         <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.18</v>
+        <v>1.59</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>3.68</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="O27" t="n">
-        <v>4.18</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S27" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF27" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>4.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>2.48</v>
+        <v>3.02</v>
       </c>
       <c r="P29" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="T29" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="U29" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.15</v>
+        <v>3.1</v>
       </c>
       <c r="M30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T30" t="n">
         <v>3.2</v>
       </c>
-      <c r="N30" t="n">
+      <c r="U30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.61</v>
       </c>
-      <c r="O30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V30" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AC30" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.1</v>
+        <v>5.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.27</v>
+        <v>1.61</v>
       </c>
       <c r="O31" t="n">
-        <v>3.99</v>
+        <v>5.75</v>
       </c>
       <c r="P31" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="R31" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U31" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V31" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.29</v>
+        <v>2.11</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,34 +4229,34 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
-        <v>3.16</v>
+        <v>4.84</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.95</v>
+        <v>2.77</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="S32" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="T32" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="V32" t="n">
         <v>8.800000000000001</v>
@@ -4265,37 +4265,37 @@
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4348,19 +4348,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="O33" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q33" t="n">
         <v>3</v>
@@ -4369,10 +4369,10 @@
         <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="T33" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
         <v>1.38</v>
@@ -4387,34 +4387,34 @@
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AA33" t="n">
         <v>2.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AG33" t="n">
         <v>1.37</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.9</v>
+        <v>2.14</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>4.95</v>
+        <v>2.48</v>
       </c>
       <c r="P34" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="T34" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="U34" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4586,61 +4586,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="O35" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
         <v>1.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.62</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.53</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE35" t="n">
         <v>2.1</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>7.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>5.9</v>
       </c>
       <c r="N37" t="n">
-        <v>2.96</v>
+        <v>1.34</v>
       </c>
       <c r="O37" t="n">
-        <v>2.65</v>
+        <v>5.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.58</v>
+        <v>1.77</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="S37" t="n">
-        <v>3.28</v>
+        <v>4.55</v>
       </c>
       <c r="T37" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="V37" t="n">
-        <v>5.8</v>
+        <v>3.72</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.92</v>
+        <v>6.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.19</v>
+        <v>3.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.54</v>
+        <v>1.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.29</v>
+        <v>3.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>7.8</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>6.05</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>1.38</v>
+        <v>2.96</v>
       </c>
       <c r="O38" t="n">
-        <v>6.1</v>
+        <v>2.65</v>
       </c>
       <c r="P38" t="n">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.77</v>
+        <v>3.58</v>
       </c>
       <c r="R38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.18</v>
       </c>
-      <c r="S38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V38" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>3.92</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.74</v>
+        <v>2.54</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="M40" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
         <v>4.17</v>
@@ -5199,10 +5199,10 @@
         <v>3.14</v>
       </c>
       <c r="R40" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S40" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="T40" t="n">
         <v>3.34</v>
@@ -5232,10 +5232,10 @@
         <v>1.62</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE40" t="n">
         <v>1.96</v>
@@ -5244,10 +5244,10 @@
         <v>1.73</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46069.89583333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -1121,17 +1121,17 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="P13" t="n">
         <v>2.02</v>
@@ -1986,28 +1986,28 @@
         <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="T13" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
         <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
         <v>2.4</v>
@@ -2016,10 +2016,10 @@
         <v>2.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
         <v>1.15</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="P14" t="n">
         <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.81</v>
+        <v>5.87</v>
       </c>
       <c r="R14" t="n">
         <v>1.48</v>
@@ -2141,7 +2141,7 @@
         <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
         <v>2.15</v>
@@ -2153,7 +2153,7 @@
         <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46069.53472222222</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
         <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="R15" t="n">
         <v>1.43</v>
@@ -2233,10 +2233,10 @@
         <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
@@ -2245,31 +2245,31 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
         <v>2.63</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="O16" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.1</v>
+        <v>4.51</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
@@ -2355,7 +2355,7 @@
         <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2364,22 +2364,22 @@
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
         <v>1.83</v>
@@ -2388,10 +2388,10 @@
         <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2459,7 +2459,7 @@
         <v>2.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>3.76</v>
       </c>
       <c r="R17" t="n">
         <v>1.27</v>
@@ -2468,10 +2468,10 @@
         <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
         <v>5</v>
@@ -2480,31 +2480,31 @@
         <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AG17" t="n">
         <v>1.21</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.99</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
         <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.08</v>
+        <v>2.51</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="R19" t="n">
         <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="T19" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
         <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.31</v>
+        <v>1.89</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="M20" t="n">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4.72</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>4.05</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>5.05</v>
       </c>
       <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.19</v>
+        <v>4.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.81</v>
+        <v>1.53</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.75</v>
+        <v>2.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.95</v>
+        <v>4.72</v>
       </c>
       <c r="P21" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>3.36</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="S21" t="n">
-        <v>2.99</v>
+        <v>2.04</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.75</v>
+        <v>2.19</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.72</v>
+        <v>2.81</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.74</v>
+        <v>5.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.69</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.81</v>
+        <v>3.43</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="M23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.3</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.66</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.66</v>
+        <v>3.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.08</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.64</v>
+        <v>2.74</v>
       </c>
       <c r="AA23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.96</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>3.12</v>
+        <v>5.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.63</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>3.42</v>
+        <v>1.7</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>3.16</v>
       </c>
       <c r="T24" t="n">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>6.1</v>
       </c>
       <c r="W24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.02</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.43</v>
+        <v>3.68</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>3.35</v>
       </c>
       <c r="M25" t="n">
-        <v>5.15</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>9.220000000000001</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>3.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA25" t="n">
         <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.22</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.59</v>
+        <v>2.14</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.68</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="M26" t="n">
         <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="O26" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="T26" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="U26" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.66</v>
+        <v>5.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46069.64583333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N30" t="n">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.99</v>
+        <v>2.48</v>
       </c>
       <c r="P30" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S30" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U30" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V30" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.15</v>
+        <v>2.56</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O31" t="n">
-        <v>5.75</v>
+        <v>3.74</v>
       </c>
       <c r="P31" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.21</v>
+        <v>3.08</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="T31" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="U31" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="V31" t="n">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.52</v>
+        <v>3.47</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.29</v>
+        <v>1.76</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.11</v>
+        <v>1.37</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.65</v>
+        <v>5.15</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG32" t="n">
         <v>2.11</v>
       </c>
-      <c r="O32" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="O33" t="n">
-        <v>3.73</v>
+        <v>3.99</v>
       </c>
       <c r="P33" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="Q33" t="n">
         <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S33" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X33" t="n">
         <v>1.03</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.44</v>
+        <v>2.86</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.14</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>2.11</v>
       </c>
       <c r="O34" t="n">
-        <v>2.48</v>
+        <v>4.84</v>
       </c>
       <c r="P34" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="S34" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="T34" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="U34" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="V34" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4705,37 +4705,37 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
         <v>2.87</v>
       </c>
       <c r="N36" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="O36" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="P36" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q36" t="n">
         <v>3.16</v>
       </c>
       <c r="R36" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="T36" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V36" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W36" t="n">
         <v>1.01</v>
@@ -4744,34 +4744,34 @@
         <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.73</v>
+        <v>4.88</v>
       </c>
       <c r="AD36" t="n">
         <v>1.17</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4827,16 +4827,16 @@
         <v>7.4</v>
       </c>
       <c r="M37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O37" t="n">
         <v>5.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q37" t="n">
         <v>1.77</v>
@@ -4845,19 +4845,19 @@
         <v>1.17</v>
       </c>
       <c r="S37" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="T37" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V37" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="W37" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
@@ -4866,31 +4866,31 @@
         <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA37" t="n">
         <v>1.33</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AE37" t="n">
         <v>1.44</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG37" t="n">
         <v>3.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.82</v>
       </c>
-      <c r="M6" t="n">
+      <c r="AC6" t="n">
         <v>3.4</v>
       </c>
-      <c r="N6" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.9</v>
+        <v>1.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,19 +1228,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.5</v>
+        <v>2.44</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>2.78</v>
       </c>
       <c r="O7" t="n">
-        <v>6.44</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.44</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>4.04</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="W8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.98</v>
+        <v>2.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,19 +1585,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>4.22</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="O10" t="n">
-        <v>4.15</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.32</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.43</v>
+        <v>2.27</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>1.69</v>
       </c>
       <c r="M11" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
         <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.72</v>
+        <v>4.84</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB11" t="n">
         <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AG11" t="n">
         <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,16 +1823,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1845,77 +1845,77 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.22</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="N12" t="n">
-        <v>1.79</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>4.15</v>
       </c>
       <c r="P12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S12" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.47</v>
-      </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.27</v>
+        <v>3.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.28</v>
+        <v>5.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,16 +2180,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>3.61</v>
       </c>
       <c r="O15" t="n">
-        <v>1.94</v>
+        <v>2.61</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.18</v>
+        <v>4.51</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.1</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.74</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.47</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,99 +2299,99 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.61</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.61</v>
+        <v>1.94</v>
       </c>
       <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2427,20 +2427,20 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,99 +2537,99 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.08</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.31</v>
+        <v>1.89</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,63 +2656,63 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.99</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>6.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.8</v>
+        <v>9.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
@@ -2721,34 +2721,34 @@
         <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.44</v>
+        <v>3.85</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.23</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.89</v>
+        <v>2.41</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46069.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,99 +2894,99 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="O21" t="n">
-        <v>4.72</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>4.05</v>
+        <v>3.16</v>
       </c>
       <c r="U21" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.81</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.75</v>
+        <v>4.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>5.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>2.78</v>
+        <v>1.69</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.88</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="V22" t="n">
-        <v>6.8</v>
+        <v>6.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.43</v>
+        <v>3.94</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>3.68</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="N23" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
-        <v>3.42</v>
+        <v>4.72</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="T23" t="n">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>5.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>2.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.27</v>
       </c>
-      <c r="M24" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N24" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>3.43</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.22</v>
+        <v>1.76</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.68</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3396,40 +3396,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
         <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>3.95</v>
+        <v>4.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="R25" t="n">
         <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
         <v>1.05</v>
@@ -3438,31 +3438,31 @@
         <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>4.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V27" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="W27" t="n">
         <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
-        <v>4.18</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB28" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF28" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="M29" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.14</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="T29" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,37 +3991,37 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.48</v>
+        <v>3.08</v>
       </c>
       <c r="P30" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
         <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T30" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W30" t="n">
         <v>1.01</v>
@@ -4030,34 +4030,34 @@
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.56</v>
+        <v>3.56</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N31" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O31" t="n">
-        <v>3.74</v>
+        <v>4.68</v>
       </c>
       <c r="P31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V31" t="n">
+        <v>10</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE31" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.15</v>
+        <v>2.56</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O32" t="n">
-        <v>5.75</v>
+        <v>3.74</v>
       </c>
       <c r="P32" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.21</v>
+        <v>3.08</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="V32" t="n">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.52</v>
+        <v>3.47</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.29</v>
+        <v>1.76</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.11</v>
+        <v>1.37</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O33" t="n">
+        <v>6</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V33" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE33" t="n">
         <v>2.27</v>
       </c>
-      <c r="O33" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.23</v>
       </c>
-      <c r="AE33" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>2.14</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.11</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>4.84</v>
+        <v>2.87</v>
       </c>
       <c r="P34" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="T34" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="M35" t="n">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="N35" t="n">
-        <v>3.49</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>3.54</v>
       </c>
       <c r="P35" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.2</v>
+        <v>3.16</v>
       </c>
       <c r="R35" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="T35" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="V35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="Z35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.4</v>
       </c>
-      <c r="AA35" t="n">
-        <v>2.53</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.7</v>
+        <v>4.88</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>2.37</v>
       </c>
       <c r="M36" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="O36" t="n">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="P36" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="S36" t="n">
-        <v>2.52</v>
+        <v>2.19</v>
       </c>
       <c r="T36" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U36" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="V36" t="n">
         <v>9.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.88</v>
+        <v>5.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -5062,34 +5062,34 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="O39" t="n">
         <v>3.65</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="S39" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T39" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
         <v>9</v>
@@ -5104,28 +5104,28 @@
         <v>1.42</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC39" t="n">
         <v>4.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
         <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
         <v>1.36</v>
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O40" t="n">
         <v>4.17</v>
@@ -5196,7 +5196,7 @@
         <v>1.81</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R40" t="n">
         <v>1.55</v>
@@ -5205,13 +5205,13 @@
         <v>2.26</v>
       </c>
       <c r="T40" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U40" t="n">
         <v>1.24</v>
       </c>
       <c r="V40" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W40" t="n">
         <v>1.03</v>
@@ -5220,31 +5220,31 @@
         <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE40" t="n">
         <v>1.96</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
         <v>1.28</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,99 +871,99 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46069.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,22 +990,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46069.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.5</v>
+        <v>1.82</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>4.04</v>
       </c>
       <c r="O6" t="n">
-        <v>6.44</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>6.75</v>
+        <v>5.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.06</v>
+        <v>1.9</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,19 +1228,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.44</v>
+        <v>5.5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.78</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>6.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,25 +1347,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>2.44</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>4.04</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.65</v>
+        <v>3.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,16 +1585,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.22</v>
+        <v>1.69</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>1.79</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>2.42</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.44</v>
+        <v>4.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
         <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.94</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,19 +1704,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="O11" t="n">
-        <v>2.42</v>
+        <v>4.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.84</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="T11" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.05</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AE11" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,19 +1823,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.1</v>
+        <v>4.22</v>
       </c>
       <c r="M12" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>1.79</v>
       </c>
       <c r="O12" t="n">
-        <v>4.15</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>1.95</v>
+        <v>2.47</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.53</v>
+        <v>2.27</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.6</v>
+        <v>4.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46069.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,25 +2180,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.61</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.61</v>
+        <v>1.94</v>
       </c>
       <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q15" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,25 +2299,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>3.61</v>
       </c>
       <c r="O16" t="n">
-        <v>1.94</v>
+        <v>2.61</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.18</v>
+        <v>4.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.1</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.74</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.47</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46069.54166666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,99 +2775,99 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.89</v>
+        <v>3.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>4.29</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46069.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,19 +3013,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.27</v>
       </c>
-      <c r="M22" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N22" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>9</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z22" t="n">
-        <v>3.94</v>
+        <v>3.43</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.68</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>2.78</v>
+        <v>5.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>4.72</v>
+        <v>1.69</v>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.01</v>
+        <v>3.16</v>
       </c>
       <c r="T23" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>13</v>
+        <v>6.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.16</v>
+        <v>3.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC23" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.12</v>
       </c>
-      <c r="AE23" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>3.68</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,99 +3251,99 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V24" t="n">
-        <v>6.8</v>
+        <v>5.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.43</v>
+        <v>4.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="M25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.4</v>
       </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.56</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>2.01</v>
       </c>
       <c r="T25" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="V25" t="n">
-        <v>6.05</v>
+        <v>13</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.19</v>
+        <v>1.66</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.72</v>
+        <v>2.16</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.01</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>5.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.16</v>
+        <v>1.54</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3617,51 +3617,51 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="M27" t="n">
         <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O27" t="n">
-        <v>4.18</v>
+        <v>4.32</v>
       </c>
       <c r="P27" t="n">
         <v>2.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="R27" t="n">
         <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="U27" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="V27" t="n">
         <v>4.1</v>
@@ -3676,10 +3676,10 @@
         <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.55</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB27" t="n">
         <v>2.87</v>
@@ -3688,16 +3688,16 @@
         <v>2.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH27" t="n">
         <v>1.13</v>
@@ -3736,57 +3736,57 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R28" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="U28" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
         <v>4.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
@@ -3816,10 +3816,10 @@
         <v>2.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46069.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,99 +3846,99 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="M29" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="O29" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T29" t="n">
         <v>3.65</v>
       </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="V29" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,63 +3965,63 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>1.61</v>
       </c>
       <c r="O30" t="n">
-        <v>3.08</v>
+        <v>6</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S30" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="W30" t="n">
         <v>1.01</v>
@@ -4033,31 +4033,31 @@
         <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,99 +4084,99 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="M31" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="N31" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="O31" t="n">
-        <v>4.68</v>
+        <v>3.65</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S31" t="n">
-        <v>2.22</v>
+        <v>2.57</v>
       </c>
       <c r="T31" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4212,57 +4212,57 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="O32" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T32" t="n">
         <v>3.08</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.94</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
@@ -4271,31 +4271,31 @@
         <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.47</v>
+        <v>3.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
         <v>1.76</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,63 +4322,63 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>3.08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T33" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V33" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.01</v>
@@ -4390,31 +4390,31 @@
         <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4450,20 +4450,20 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -4582,38 +4582,38 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.85</v>
+        <v>3.46</v>
       </c>
       <c r="M35" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
         <v>2.25</v>
       </c>
       <c r="O35" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="P35" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S35" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="T35" t="n">
         <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
         <v>9.5</v>
@@ -4622,7 +4622,7 @@
         <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y35" t="n">
         <v>1.43</v>
@@ -4631,28 +4631,28 @@
         <v>2.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.88</v>
+        <v>4.22</v>
       </c>
       <c r="AD35" t="n">
         <v>1.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG35" t="n">
         <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4691,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -4701,62 +4701,62 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="M36" t="n">
         <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>3.35</v>
+        <v>3.51</v>
       </c>
       <c r="O36" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
         <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S36" t="n">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="T36" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="U36" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
         <v>2.38</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AB36" t="n">
         <v>1.44</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="AD36" t="n">
         <v>1.13</v>
@@ -4765,13 +4765,13 @@
         <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O37" t="n">
         <v>6</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O37" t="n">
-        <v>5.75</v>
       </c>
       <c r="P37" t="n">
         <v>2.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T37" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="V37" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AD37" t="n">
         <v>1.91</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG37" t="n">
         <v>3.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46069.70833333334</v>
@@ -4926,78 +4926,78 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L38" t="n">
         <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P38" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S38" t="n">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V38" t="n">
-        <v>5.8</v>
+        <v>5.55</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.92</v>
+        <v>4.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE38" t="n">
         <v>1.6</v>
@@ -5006,10 +5006,10 @@
         <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46069.70833333334</v>
@@ -5045,30 +5045,30 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L39" t="n">
         <v>2.98</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="O39" t="n">
         <v>3.65</v>
@@ -5080,16 +5080,16 @@
         <v>2.9</v>
       </c>
       <c r="R39" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
         <v>9</v>
@@ -5098,10 +5098,10 @@
         <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z39" t="n">
         <v>2.8</v>
@@ -5110,7 +5110,7 @@
         <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
         <v>4.2</v>
@@ -5119,13 +5119,13 @@
         <v>1.22</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AH39" t="n">
         <v>1.36</v>

--- a/jogos_2026-02-16.xlsx
+++ b/jogos_2026-02-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,22 +871,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46069.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46069.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.82</v>
+        <v>2.44</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>4.04</v>
+        <v>2.78</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.65</v>
+        <v>3.98</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,25 +1228,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.5</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>4.04</v>
       </c>
       <c r="O7" t="n">
-        <v>6.44</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>6.75</v>
+        <v>5.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.9</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,19 +1347,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.44</v>
+        <v>5.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>6.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46069.41666666666</v>
@@ -1585,19 +1585,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="O10" t="n">
-        <v>2.42</v>
+        <v>4.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.84</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="S10" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="T10" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AE10" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46069.5</v>
@@ -1704,19 +1704,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>1.69</v>
       </c>
       <c r="M11" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.15</v>
+        <v>2.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>4.84</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="T11" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC11" t="n">
         <v>4.2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AD11" t="n">
         <v>1.15</v>
       </c>
-      <c r="V11" t="n">
-        <v>15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AE11" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>1.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46069.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,19 +3013,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.21</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.78</v>
+        <v>4.72</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.01</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.43</v>
+        <v>2.16</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.01</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46069.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,19 +3132,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.27</v>
       </c>
-      <c r="M23" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.94</v>
+        <v>3.43</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.68</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46069.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,25 +3251,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>5.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="T24" t="n">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="U24" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>5.05</v>
+        <v>6.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>2.24</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>3.68</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46069.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,25 +3370,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.4</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
         <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.01</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="V25" t="n">
-        <v>13</v>
+        <v>5.05</v>
       </c>
       <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.03</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.66</v>
+        <v>1.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.16</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.95</v>
+        <v>2.59</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46069.625</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,99 +3846,99 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3</v>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O29" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>2.22</v>
+        <v>2.57</v>
       </c>
       <c r="T29" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46069.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,99 +3965,99 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.25</v>
+        <v>3.56</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N30" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O30" t="n">
-        <v>6</v>
+        <v>4.68</v>
       </c>
       <c r="P30" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="T30" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="U30" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V30" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="W30" t="n">
         <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46069.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,16 +4084,16 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>2</v>
@@ -4102,7 +4102,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4110,34 +4110,34 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="P31" t="n">
         <v>2</v>
       </c>
       <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T31" t="n">
         <v>3</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
         <v>8.5</v>
@@ -4146,37 +4146,37 @@
         <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
         <v>1.59</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="AD31" t="n">
         <v>1.17</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46069.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4218,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.82</v>
+        <v>5.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.61</v>
+        <v>1.61</v>
       </c>
       <c r="O32" t="n">
+        <v>6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T32" t="n">
         <v>3.4</v>
       </c>
-      <c r="P32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.08</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.76</v>
+        <v>2.27</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46069.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,25 +4322,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4348,37 +4348,37 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q33" t="n">
         <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.01</v>
@@ -4387,34 +4387,34 @@
         <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46069.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.14</v>
+        <v>2.82</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O34" t="n">
         <v>3.4</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.87</v>
-      </c>
       <c r="P34" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="T34" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="U34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46069.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,19 +4560,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.46</v>
+        <v>2.31</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>3.51</v>
       </c>
       <c r="O35" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="S35" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.22</v>
+        <v>4.65</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG35" t="n">
         <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46069.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,19 +4679,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.31</v>
+        <v>3.46</v>
       </c>
       <c r="M36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2.9</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
       <c r="R36" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="S36" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="T36" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V36" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.65</v>
+        <v>4.22</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG36" t="n">
         <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46069.69791666666</v>
@@ -5181,19 +5181,19 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="N40" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="P40" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>3.1</v>
@@ -5211,7 +5211,7 @@
         <v>1.24</v>
       </c>
       <c r="V40" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="W40" t="n">
         <v>1.03</v>
@@ -5223,22 +5223,22 @@
         <v>1.42</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF40" t="n">
         <v>1.7</v>
